--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -80,40 +80,40 @@
     <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.46907424926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.1964373588562</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752062797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78871870040894</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304004669189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">7.86292886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.73062038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -689,31 +689,31 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,34 +839,34 @@
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.59773445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.48905181884766</t>
@@ -908,52 +908,52 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.42762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
+    <t xml:space="preserve">4.92378091812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.3360743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486404418945</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33532,7 +33532,7 @@
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
-        <v>45943.6456365741</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1202" t="n">
         <v>3750</v>
@@ -33553,6 +33553,32 @@
         <v>650</v>
       </c>
       <c r="H1202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>45944.6494444444</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>647</v>
+      </c>
+      <c r="H1203" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
+    <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
     <t xml:space="preserve">3.3191237449646</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,34 +89,34 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284504890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871870040894</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.68530440330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.67629742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
+    <t xml:space="preserve">5.76488733291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.88183069229126</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853425979614</t>
+    <t xml:space="preserve">7.93853378295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.51148843765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.13346242904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
+    <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
+    <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038202285767</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
+    <t xml:space="preserve">5.79324054718018</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
+    <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883262634277</t>
+    <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795316696167</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465721130371</t>
+    <t xml:space="preserve">4.62608623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465768814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">3.93146419525146</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663991928101</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993635177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663944244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927513122559</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915547370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.79915571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080368995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360743522644</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
+    <t xml:space="preserve">3.24156808853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33558,13 +33558,13 @@
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
-        <v>45944.6494444444</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1203" t="n">
         <v>2200</v>
       </c>
       <c r="C1203" t="n">
-        <v>1.10000002384186</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="D1203" t="n">
         <v>1.07500004768372</v>
@@ -33579,6 +33579,32 @@
         <v>647</v>
       </c>
       <c r="H1203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>45945.6064930556</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>11990</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>648</v>
+      </c>
+      <c r="H1204" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -56,19 +56,19 @@
     <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
+    <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29985117912292</t>
+    <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973756790161</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.76051449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752062797546</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.68530440330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.67629766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488733291626</t>
+    <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.51148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.13346290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038202285767</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324054718018</t>
+    <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
+    <t xml:space="preserve">5.43411540985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
+    <t xml:space="preserve">4.67333984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795316696167</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
+    <t xml:space="preserve">4.62608671188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993635177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663944244385</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993587493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927513122559</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.79915547370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360743522644</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
+    <t xml:space="preserve">3.87476062774658</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33584,7 +33584,7 @@
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
-        <v>45945.6064930556</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1204" t="n">
         <v>11990</v>
@@ -33605,6 +33605,32 @@
         <v>648</v>
       </c>
       <c r="H1204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>45946.58</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>110</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>650</v>
+      </c>
+      <c r="H1205" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033576965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
+    <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129118919373</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009383201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.61009359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949515342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.22464084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692218780518</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -164,22 +164,22 @@
     <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80752062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78871870040894</t>
+    <t xml:space="preserve">3.80752086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350789070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308722496033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.71350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,58 +377,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,52 +446,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.37917947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.43411588668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
+    <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -833,37 +833,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -878,91 +878,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,43 +992,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421130180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.87476086616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -1968,6 +1968,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.08500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08000004291534</t>
   </si>
 </sst>
 </file>
@@ -33662,13 +33665,13 @@
     </row>
     <row r="1207">
       <c r="A1207" s="1" t="n">
-        <v>45950.649537037</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1207" t="n">
         <v>8960</v>
       </c>
       <c r="C1207" t="n">
-        <v>1.09500002861023</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="D1207" t="n">
         <v>1.06500005722046</v>
@@ -33683,6 +33686,32 @@
         <v>647</v>
       </c>
       <c r="H1207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>45951.4934837963</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>7307</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G1208" t="s">
+        <v>652</v>
+      </c>
+      <c r="H1208" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -50,52 +50,52 @@
     <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590260505676</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206835746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.42206811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266703605652</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608109474182</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.78871822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
+    <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -33717,7 +33717,7 @@
     </row>
     <row r="1209">
       <c r="A1209" s="1" t="n">
-        <v>45952.6069675926</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1209" t="n">
         <v>4484</v>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1974,6 +1974,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.07000005245209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05499994754791</t>
   </si>
 </sst>
 </file>
@@ -33772,7 +33775,7 @@
     </row>
     <row r="1211">
       <c r="A1211" s="1" t="n">
-        <v>45954.5124189815</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1211" t="n">
         <v>1251</v>
@@ -33793,6 +33796,32 @@
         <v>652</v>
       </c>
       <c r="H1211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>45957.6911111111</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>9134</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="G1212" t="s">
+        <v>654</v>
+      </c>
+      <c r="H1212" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009359359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.61009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949515342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -116,34 +116,34 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.76051449775696</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -179,34 +179,34 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231077194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69470524787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.73231053352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69470548629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
+    <t xml:space="preserve">3.59124159812927</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -356,28 +356,28 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007953643799</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.44533395767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
+    <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03895616531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.78378915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03895664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
+    <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.28467273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137725830078</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15236473083496</t>
+    <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412317276001</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.56642436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.70641660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630590438843</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146467208862</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509123802185</t>
+    <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10157680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10157632827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
+    <t xml:space="preserve">3.30772280693054</t>
   </si>
   <si>
     <t xml:space="preserve">3.15651249885559</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11871004104614</t>
+    <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
     <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
+    <t xml:space="preserve">3.26046943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.23211765289307</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
+    <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -1977,6 +1977,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.05499994754791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07500004768372</t>
   </si>
 </sst>
 </file>
@@ -33801,7 +33804,7 @@
     </row>
     <row r="1212">
       <c r="A1212" s="1" t="n">
-        <v>45957.6911111111</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1212" t="n">
         <v>9134</v>
@@ -33822,6 +33825,32 @@
         <v>654</v>
       </c>
       <c r="H1212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>45958.5662731481</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>655</v>
+      </c>
+      <c r="H1213" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284504890442</t>
+    <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164721488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6006920337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92973709106445</t>
+    <t xml:space="preserve">3.60069227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.78871822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
+    <t xml:space="preserve">6.9840202331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
+    <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
+    <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
+    <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.64379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851873397827</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.34137630462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">6.06730890274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.62608575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
+    <t xml:space="preserve">4.03542184829712</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
+    <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
+    <t xml:space="preserve">4.9521336555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.04663991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -33853,7 +33853,7 @@
     </row>
     <row r="1214">
       <c r="A1214" s="1" t="n">
-        <v>45959.5582638889</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1214" t="n">
         <v>1160</v>
@@ -33874,6 +33874,32 @@
         <v>652</v>
       </c>
       <c r="H1214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>45960.5074768519</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>5718</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>654</v>
+      </c>
+      <c r="H1215" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.82085561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590260505676</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.61009335517883</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.19643759727478</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404216766357</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487228393555</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.50027084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622577667236</t>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.39216423034668</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.39039707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774585723877</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137630462646</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.26577234268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115394592285</t>
+    <t xml:space="preserve">6.00115346908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
+    <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
+    <t xml:space="preserve">5.70818376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247591018677</t>
+    <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.53630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59300947189331</t>
+    <t xml:space="preserve">4.60245943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58355855941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59300899505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.73476934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
+    <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
+    <t xml:space="preserve">3.95036554336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
+    <t xml:space="preserve">4.53157949447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.46542596817017</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75366973876953</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -33879,7 +33879,7 @@
     </row>
     <row r="1215">
       <c r="A1215" s="1" t="n">
-        <v>45960.5074768519</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1215" t="n">
         <v>5718</v>
@@ -33900,6 +33900,32 @@
         <v>654</v>
       </c>
       <c r="H1215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>45961.5223148148</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>11353</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>654</v>
+      </c>
+      <c r="H1216" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -56,40 +56,40 @@
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.67590284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009335517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248878479004</t>
+    <t xml:space="preserve">3.61009359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949467658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.5254819393158</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643759727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.76991581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.6853039264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33905,7 +33905,7 @@
     </row>
     <row r="1216">
       <c r="A1216" s="1" t="n">
-        <v>45961.5223148148</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1216" t="n">
         <v>11353</v>
@@ -33926,6 +33926,32 @@
         <v>654</v>
       </c>
       <c r="H1216" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>45964.6766550926</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>5079</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>652</v>
+      </c>
+      <c r="H1217" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
+    <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129095077515</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.40326547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350765228271</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6853039264679</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.51563692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565292358398</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">7.9385347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76842355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.76842260360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709287643433</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
+    <t xml:space="preserve">5.80269002914429</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15236473083496</t>
+    <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.32247591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.53807258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.70641660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
+    <t xml:space="preserve">4.53630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.62136077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
+    <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">3.90311288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926736831665</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.32839107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.24333524703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -1977,6 +1977,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.07500004768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06500005722046</t>
   </si>
 </sst>
 </file>
@@ -33931,7 +33934,7 @@
     </row>
     <row r="1217">
       <c r="A1217" s="1" t="n">
-        <v>45964.6766550926</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1217" t="n">
         <v>5079</v>
@@ -33952,6 +33955,32 @@
         <v>652</v>
       </c>
       <c r="H1217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>45965.6911689815</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>6160</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>655</v>
+      </c>
+      <c r="H1218" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.61949467658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.76991581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.51563668251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402799606323</t>
+    <t xml:space="preserve">7.84402894973755</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">7.80622625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">7.9385347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76842260360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
+    <t xml:space="preserve">6.73830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
+    <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1523642539978</t>
+    <t xml:space="preserve">6.15236473083496</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
+    <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">6.02950572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74598693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.7459864616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
+    <t xml:space="preserve">6.32247543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.07675933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.70641708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39454555511475</t>
+    <t xml:space="preserve">4.62136125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
+    <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90311288833618</t>
+    <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926736831665</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.32839155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333524703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.24333572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.77080368995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33960,7 +33960,7 @@
     </row>
     <row r="1218">
       <c r="A1218" s="1" t="n">
-        <v>45965.6911689815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1218" t="n">
         <v>6160</v>
@@ -33981,6 +33981,32 @@
         <v>655</v>
       </c>
       <c r="H1218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>45966.6833912037</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>655</v>
+      </c>
+      <c r="H1219" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="657">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.54428505897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242462158203</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344348907471</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -1980,6 +1980,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.06500005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05999994277954</t>
   </si>
 </sst>
 </file>
@@ -33986,10 +33989,10 @@
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
-        <v>45966.6833912037</v>
+        <v>45967.6722106481</v>
       </c>
       <c r="B1219" t="n">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="C1219" t="n">
         <v>1.06500005722046</v>
@@ -33998,13 +34001,13 @@
         <v>1.03999996185303</v>
       </c>
       <c r="E1219" t="n">
-        <v>1.03999996185303</v>
+        <v>1.06500005722046</v>
       </c>
       <c r="F1219" t="n">
-        <v>1.06500005722046</v>
+        <v>1.05999994277954</v>
       </c>
       <c r="G1219" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590260505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632374763489</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350765228271</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6853039264679</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">3.85585927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565292358398</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
+    <t xml:space="preserve">5.50027084350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
+    <t xml:space="preserve">8.39216423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.76665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
+    <t xml:space="preserve">7.39039707183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577234268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1523642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.29412364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
+    <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
+    <t xml:space="preserve">4.60245943069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
+    <t xml:space="preserve">4.73476934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.48905181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036554336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.53157949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75366973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33989,19 +33989,19 @@
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
-        <v>45967.6722106481</v>
+        <v>45968.4919097222</v>
       </c>
       <c r="B1219" t="n">
-        <v>2100</v>
+        <v>1050</v>
       </c>
       <c r="C1219" t="n">
-        <v>1.06500005722046</v>
+        <v>1.05999994277954</v>
       </c>
       <c r="D1219" t="n">
         <v>1.03999996185303</v>
       </c>
       <c r="E1219" t="n">
-        <v>1.06500005722046</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="F1219" t="n">
         <v>1.05999994277954</v>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,40 +47,40 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
+    <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650128364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428458213806</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248878479004</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632327079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.62889623641968</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.97456979751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -365,82 +365,82 @@
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.44533395767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">5.78378915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.28467273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -812,40 +812,40 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.45124959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.42762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.32662391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.14706158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
+    <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
+    <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -33989,27 +33989,105 @@
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
-        <v>45968.4919097222</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1219" t="n">
-        <v>1050</v>
+        <v>2750</v>
       </c>
       <c r="C1219" t="n">
-        <v>1.05999994277954</v>
+        <v>1.06500005722046</v>
       </c>
       <c r="D1219" t="n">
         <v>1.03999996185303</v>
       </c>
       <c r="E1219" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>655</v>
+      </c>
+      <c r="H1219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G1220" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1221" t="n">
         <v>1.04999995231628</v>
       </c>
-      <c r="F1219" t="n">
+      <c r="F1221" t="n">
         <v>1.05999994277954</v>
       </c>
-      <c r="G1219" t="s">
+      <c r="G1221" t="s">
         <v>656</v>
       </c>
-      <c r="H1219" t="s">
+      <c r="H1221" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>45971.3695023148</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1222" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="659">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033576965332</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
+    <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129118919373</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009359359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949515342712</t>
+    <t xml:space="preserve">3.61009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57248854637146</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284504890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.25284481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -125,58 +125,58 @@
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763495445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29985117912292</t>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752086639404</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76051449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632374763489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350812911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710043907166</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
+    <t xml:space="preserve">3.68530440330505</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
+    <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,58 +377,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,52 +446,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379692077637</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -833,37 +833,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -878,91 +878,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.3945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,43 +992,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.93323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.88421154022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.47783398628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -1986,6 +1986,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.05999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02499997615814</t>
   </si>
 </sst>
 </file>
@@ -34096,7 +34099,7 @@
     </row>
     <row r="1223">
       <c r="A1223" s="1" t="n">
-        <v>45972.6503935185</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1223" t="n">
         <v>750</v>
@@ -34117,6 +34120,32 @@
         <v>654</v>
       </c>
       <c r="H1223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>45973.6911805556</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>17780</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>658</v>
+      </c>
+      <c r="H1224" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033576965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,43 +77,43 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428458213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009383201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949515342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.1964373588562</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2246413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763471603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2998514175415</t>
+    <t xml:space="preserve">3.22464084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763495445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692218780518</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752062797546</t>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350789070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308722496033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.71350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530440330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.6853039264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,58 +377,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,52 +446,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.37917947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.43411588668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
+    <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -833,37 +833,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -878,91 +878,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,43 +992,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421130180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.87476086616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34183,7 +34183,7 @@
     </row>
     <row r="1226">
       <c r="A1226" s="1" t="n">
-        <v>45975.6818865741</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1226" t="n">
         <v>11620</v>
@@ -34204,6 +34204,32 @@
         <v>660</v>
       </c>
       <c r="H1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>45978.5128356481</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>3031</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>660</v>
+      </c>
+      <c r="H1227" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153384208679</t>
+    <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
+    <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.54428505897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,34 +89,34 @@
     <t xml:space="preserve">3.61949467658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.57248830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42206811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46907448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.40326547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667977333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42206835746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242438316345</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308722496033</t>
+    <t xml:space="preserve">3.56308746337891</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
+    <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470524787903</t>
+    <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">3.85585927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565292358398</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
+    <t xml:space="preserve">5.50027084350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
+    <t xml:space="preserve">8.39216423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.76665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
+    <t xml:space="preserve">7.39039707183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577234268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1523642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.29412364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
+    <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
+    <t xml:space="preserve">4.60245943069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
+    <t xml:space="preserve">4.73476934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.48905181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036554336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.53157949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75366973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34287,7 +34287,7 @@
     </row>
     <row r="1230">
       <c r="A1230" s="1" t="n">
-        <v>45981.6912615741</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1230" t="n">
         <v>580</v>
@@ -34308,6 +34308,32 @@
         <v>658</v>
       </c>
       <c r="H1230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>45982.6334490741</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>6620</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>659</v>
+      </c>
+      <c r="H1231" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
+    <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,34 +89,34 @@
     <t xml:space="preserve">3.61949467658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42206835746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42206811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242438316345</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973756790161</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
+    <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -1995,6 +1995,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.00499999523163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
 </sst>
 </file>
@@ -34313,7 +34316,7 @@
     </row>
     <row r="1231">
       <c r="A1231" s="1" t="n">
-        <v>45982.6334490741</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1231" t="n">
         <v>6620</v>
@@ -34334,6 +34337,32 @@
         <v>659</v>
       </c>
       <c r="H1231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>45985.6911921296</v>
+      </c>
+      <c r="B1232" t="n">
+        <v>4884</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>661</v>
+      </c>
+      <c r="H1232" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="663">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650152206421</t>
+    <t xml:space="preserve">3.66650128364563</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129095077515</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548241615295</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.40326547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.92973685264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7605140209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350765228271</t>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
@@ -182,31 +182,31 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
+    <t xml:space="preserve">3.59124159812927</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007953643799</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.44533395767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
+    <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03895616531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.78378915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03895664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
+    <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.28467273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137725830078</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15236473083496</t>
+    <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412317276001</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.56642436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.70641660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630590438843</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146467208862</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509123802185</t>
+    <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10157680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10157632827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
+    <t xml:space="preserve">3.30772280693054</t>
   </si>
   <si>
     <t xml:space="preserve">3.15651249885559</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11871004104614</t>
+    <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
     <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
+    <t xml:space="preserve">3.26046943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.23211765289307</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
+    <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -1998,6 +1998,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00999999046326</t>
   </si>
 </sst>
 </file>
@@ -34342,7 +34345,7 @@
     </row>
     <row r="1232">
       <c r="A1232" s="1" t="n">
-        <v>45985.6911921296</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1232" t="n">
         <v>4884</v>
@@ -34351,7 +34354,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="D1232" t="n">
-        <v>1.00999999046326</v>
+        <v>1</v>
       </c>
       <c r="E1232" t="n">
         <v>1.05999994277954</v>
@@ -34363,6 +34366,32 @@
         <v>661</v>
       </c>
       <c r="H1232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>45986.6911689815</v>
+      </c>
+      <c r="B1233" t="n">
+        <v>1762</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G1233" t="s">
+        <v>662</v>
+      </c>
+      <c r="H1233" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="664">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,34 +50,34 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650128364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548241615295</t>
+    <t xml:space="preserve">3.57248878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973685264587</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
+    <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.62889623641968</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014270782471</t>
+    <t xml:space="preserve">3.63849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728489875793</t>
+    <t xml:space="preserve">3.51563692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.76135325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4985032081604</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697441101074</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
+    <t xml:space="preserve">7.57941007614136</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">7.80622577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216613769531</t>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326431274414</t>
+    <t xml:space="preserve">8.22205257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
+    <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698993682861</t>
+    <t xml:space="preserve">7.61721277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270650863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.35082721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895664215088</t>
+    <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
+    <t xml:space="preserve">5.80269002914429</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654378890991</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467273712158</t>
+    <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
+    <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257204055786</t>
+    <t xml:space="preserve">4.47960138320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883262634277</t>
+    <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
+    <t xml:space="preserve">4.55520677566528</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.62136077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311288833618</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.32839107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.3266236782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
+    <t xml:space="preserve">3.02420353889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2001,6 +2001,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.00999999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01999998092651</t>
   </si>
 </sst>
 </file>
@@ -34371,7 +34374,7 @@
     </row>
     <row r="1233">
       <c r="A1233" s="1" t="n">
-        <v>45986.6911689815</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1233" t="n">
         <v>1762</v>
@@ -34392,6 +34395,32 @@
         <v>662</v>
       </c>
       <c r="H1233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>45987.5988425926</v>
+      </c>
+      <c r="B1234" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>663</v>
+      </c>
+      <c r="H1234" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.82085561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590260505676</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.61009335517883</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.19643759727478</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404216766357</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487228393555</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.50027084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622577667236</t>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.39216423034668</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.39039707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774585723877</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137630462646</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.26577234268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115394592285</t>
+    <t xml:space="preserve">6.00115346908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
+    <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
+    <t xml:space="preserve">5.70818376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247591018677</t>
+    <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.53630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59300947189331</t>
+    <t xml:space="preserve">4.60245943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58355855941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59300899505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.73476934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
+    <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
+    <t xml:space="preserve">3.95036554336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
+    <t xml:space="preserve">4.53157949447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.46542596817017</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75366973876953</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -34400,7 +34400,7 @@
     </row>
     <row r="1234">
       <c r="A1234" s="1" t="n">
-        <v>45987.5988425926</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1234" t="n">
         <v>1580</v>
@@ -34421,6 +34421,32 @@
         <v>663</v>
       </c>
       <c r="H1234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>45988.3568055556</v>
+      </c>
+      <c r="B1235" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1235" t="s">
+        <v>657</v>
+      </c>
+      <c r="H1235" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="665">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.82085585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">3.9203360080719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
+    <t xml:space="preserve">3.67590308189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129118919373</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009335517883</t>
+    <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.57248830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206811904907</t>
+    <t xml:space="preserve">3.42206835746765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19643759727478</t>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -125,16 +125,16 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763447761536</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.78871846199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853039264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304004669189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">7.86292886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.73062038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -836,34 +836,34 @@
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.59773445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.48905181884766</t>
@@ -905,52 +905,52 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.42762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -989,25 +989,25 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
+    <t xml:space="preserve">4.92378091812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.3360743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486404418945</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2004,6 +2004,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.01999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04499995708466</t>
   </si>
 </sst>
 </file>
@@ -34426,7 +34429,7 @@
     </row>
     <row r="1235">
       <c r="A1235" s="1" t="n">
-        <v>45988.3568055556</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1235" t="n">
         <v>1020</v>
@@ -34447,6 +34450,32 @@
         <v>657</v>
       </c>
       <c r="H1235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>45989.3335069444</v>
+      </c>
+      <c r="B1236" t="n">
+        <v>170</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="G1236" t="s">
+        <v>664</v>
+      </c>
+      <c r="H1236" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -56,19 +56,19 @@
     <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453722000122</t>
+    <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.23404240608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2998514175415</t>
+    <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.76051425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752062797546</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.68530440330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.67629742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
+    <t xml:space="preserve">5.76488733291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.88183069229126</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853425979614</t>
+    <t xml:space="preserve">7.93853378295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.51148843765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.13346242904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
+    <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
+    <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038202285767</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
+    <t xml:space="preserve">5.79324054718018</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
+    <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883262634277</t>
+    <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795316696167</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465721130371</t>
+    <t xml:space="preserve">4.62608623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465768814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">3.93146419525146</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663991928101</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993635177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663944244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927513122559</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915547370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.79915571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080368995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360743522644</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
+    <t xml:space="preserve">3.24156808853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34591,7 +34591,7 @@
     </row>
     <row r="1241">
       <c r="A1241" s="1" t="n">
-        <v>45996.5090162037</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1241" t="n">
         <v>5020</v>
@@ -34612,6 +34612,32 @@
         <v>664</v>
       </c>
       <c r="H1241" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>45999.5636921296</v>
+      </c>
+      <c r="B1242" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>666</v>
+      </c>
+      <c r="H1242" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -56,19 +56,19 @@
     <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
+    <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29985117912292</t>
+    <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973756790161</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.76051449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752062797546</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.68530440330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.67629766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488733291626</t>
+    <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.51148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.13346290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038202285767</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324054718018</t>
+    <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
+    <t xml:space="preserve">5.43411540985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
+    <t xml:space="preserve">4.67333984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795316696167</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
+    <t xml:space="preserve">4.62608671188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993635177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663944244385</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993587493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927513122559</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.79915547370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360743522644</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
+    <t xml:space="preserve">3.87476062774658</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34617,7 +34617,7 @@
     </row>
     <row r="1242">
       <c r="A1242" s="1" t="n">
-        <v>45999.5636921296</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1242" t="n">
         <v>21</v>
@@ -34638,6 +34638,32 @@
         <v>666</v>
       </c>
       <c r="H1242" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>46000.3888657407</v>
+      </c>
+      <c r="B1243" t="n">
+        <v>1219</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>659</v>
+      </c>
+      <c r="H1243" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.82085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78871846199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76051425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78871822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530440330505</t>
+    <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.69470524787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
+    <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -242,37 +242,37 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.65148067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -308,28 +308,28 @@
     <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,67 +377,67 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
     <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">8.14644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952173233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.23742008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302499771118</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1523642539978</t>
+    <t xml:space="preserve">6.15236473083496</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
+    <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">5.94445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5758752822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.56642484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57587575912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
+    <t xml:space="preserve">5.31125783920288</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.70641708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
+    <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -878,46 +878,46 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47015142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,34 +926,34 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10157632827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12520265579224</t>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10157680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
+    <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
+    <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.88421177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,46 +1085,46 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
+    <t xml:space="preserve">3.32662391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
     <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.7140998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
+    <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.23211765289307</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -34643,7 +34643,7 @@
     </row>
     <row r="1243">
       <c r="A1243" s="1" t="n">
-        <v>46000.3888657407</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1243" t="n">
         <v>1219</v>
@@ -34664,6 +34664,32 @@
         <v>659</v>
       </c>
       <c r="H1243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46001.6910185185</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>6020</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>666</v>
+      </c>
+      <c r="H1244" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -34744,7 +34744,7 @@
     </row>
     <row r="1247">
       <c r="A1247" s="1" t="n">
-        <v>46006.6380208333</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1247" t="n">
         <v>1645</v>
@@ -34765,6 +34765,32 @@
         <v>659</v>
       </c>
       <c r="H1247" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46007.6912037037</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>42</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>658</v>
+      </c>
+      <c r="H1248" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.82085585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033576965332</t>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
+    <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.54428505897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949515342712</t>
+    <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57248854637146</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625863075256</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284504890442</t>
+    <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
     <t xml:space="preserve">3.1964373588562</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763495445251</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350812911987</t>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308746337891</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290921211243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.72290897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487228393555</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
@@ -275,22 +275,22 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.50027084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622577667236</t>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.39216423034668</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -488,31 +488,31 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.39039707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -533,19 +533,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774585723877</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137630462646</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.26577234268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115394592285</t>
+    <t xml:space="preserve">6.00115346908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
+    <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
+    <t xml:space="preserve">5.70818376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247591018677</t>
+    <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.53630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59300947189331</t>
+    <t xml:space="preserve">4.60245943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58355855941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59300899505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.73476934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
+    <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
+    <t xml:space="preserve">3.95036554336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
+    <t xml:space="preserve">4.53157949447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.46542596817017</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75366973876953</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -34797,6 +34797,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>659</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46009.6861226852</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>663</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.59129095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.57248878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254819393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164769172668</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29985117912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.2998514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
+    <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -305,31 +305,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -854,28 +854,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -923,34 +923,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1079,28 +1079,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34825,7 +34825,7 @@
     </row>
     <row r="1250">
       <c r="A1250" s="1" t="n">
-        <v>46009.6861226852</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B1250" t="n">
         <v>1995</v>
@@ -34846,6 +34846,32 @@
         <v>663</v>
       </c>
       <c r="H1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46010.6099421296</v>
+      </c>
+      <c r="B1251" t="n">
+        <v>4530</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>0.994000017642975</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>663</v>
+      </c>
+      <c r="H1251" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -50,34 +50,34 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650128364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548241615295</t>
+    <t xml:space="preserve">3.57248878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973685264587</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
+    <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.62889623641968</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014270782471</t>
+    <t xml:space="preserve">3.63849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728489875793</t>
+    <t xml:space="preserve">3.51563692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.76135325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4985032081604</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697441101074</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
+    <t xml:space="preserve">7.57941007614136</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">7.80622577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216613769531</t>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326431274414</t>
+    <t xml:space="preserve">8.22205257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
+    <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698993682861</t>
+    <t xml:space="preserve">7.61721277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270650863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.35082721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895664215088</t>
+    <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
+    <t xml:space="preserve">5.80269002914429</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654378890991</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467273712158</t>
+    <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
+    <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257204055786</t>
+    <t xml:space="preserve">4.47960138320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883262634277</t>
+    <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
+    <t xml:space="preserve">4.55520677566528</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.62136077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311288833618</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.32839107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.3266236782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
+    <t xml:space="preserve">3.02420353889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -34874,7 +34874,7 @@
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
-        <v>46013.64875</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B1252" t="n">
         <v>4180</v>
@@ -34895,6 +34895,32 @@
         <v>659</v>
       </c>
       <c r="H1252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46014.5819675926</v>
+      </c>
+      <c r="B1253" t="n">
+        <v>6911</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>665</v>
+      </c>
+      <c r="H1253" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
+    <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -74,64 +74,64 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625863075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763495445251</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752086639404</t>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350789070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.71350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.67629742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.29235649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
+    <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
     <t xml:space="preserve">7.93853378295898</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.39039754867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.51148843765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
+    <t xml:space="preserve">6.13346242904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466497421265</t>
+    <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.07675838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.79324054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.59773445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56465721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.56465768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091534614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926689147949</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.75367069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
+    <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718900680542</t>
+    <t xml:space="preserve">5.03718852996826</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.04663944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321654319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24156832695007</t>
+    <t xml:space="preserve">3.77080368995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321630477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24156808853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -34952,7 +34952,7 @@
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
-        <v>46021.6924652778</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1255" t="n">
         <v>26024</v>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -50,16 +50,16 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74517560005188</t>
+    <t xml:space="preserve">2.7451753616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033624649048</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326523780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42206811904907</t>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42206835746765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.51608109474182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.92973709106445</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308722496033</t>
+    <t xml:space="preserve">3.56308746337891</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470524787903</t>
+    <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
+    <t xml:space="preserve">6.9840202331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
+    <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
+    <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
+    <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.64379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851873397827</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.34137630462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">6.06730890274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.62608575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
+    <t xml:space="preserve">4.03542184829712</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
+    <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
+    <t xml:space="preserve">4.9521336555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.04663991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -34978,7 +34978,7 @@
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
-        <v>46024.6801157407</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1256" t="n">
         <v>3990</v>
@@ -34999,6 +34999,32 @@
         <v>659</v>
       </c>
       <c r="H1256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="n">
+        <v>46027.420474537</v>
+      </c>
+      <c r="B1257" t="n">
+        <v>137</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1257" t="s">
+        <v>659</v>
+      </c>
+      <c r="H1257" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033576965332</t>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009359359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949515342712</t>
+    <t xml:space="preserve">3.61009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57248854637146</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284504890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80752086639404</t>
+    <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350812911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.71350789070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.68530440330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.67629742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992811203003</t>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
@@ -323,19 +323,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292934417725</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
+    <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
+    <t xml:space="preserve">6.51148843765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
+    <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -587,43 +587,43 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
+    <t xml:space="preserve">6.13346242904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.64379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851873397827</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
+    <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466497421265</t>
+    <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
+    <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06730890274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">6.06730842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.62608623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
+    <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,28 +923,28 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
+    <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.75367069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9521336555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718900680542</t>
+    <t xml:space="preserve">4.95213317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718852996826</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.04663944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
+    <t xml:space="preserve">3.24156808853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -35031,6 +35031,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="n">
+        <v>46028.3333333333</v>
+      </c>
+      <c r="B1258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>660</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="1" t="n">
+        <v>46029.6747453704</v>
+      </c>
+      <c r="B1259" t="n">
+        <v>9881</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>0.973999977111816</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1259" t="s">
+        <v>664</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.9203360080719</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009383201599</t>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625863075256</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.22464108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81692218780518</t>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752062797546</t>
+    <t xml:space="preserve">3.82632374763489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308722496033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530440330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.56308746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.67629766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5002703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.29235601425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50027084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
+    <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
     <t xml:space="preserve">7.93853378295898</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.39039707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.51148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.73830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.97280263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
+    <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
+    <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.26577234268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115394592285</t>
+    <t xml:space="preserve">6.00115346908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
+    <t xml:space="preserve">5.70818376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
+    <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247591018677</t>
+    <t xml:space="preserve">5.94445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
+    <t xml:space="preserve">6.07675933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.79324007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.53630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245990753174</t>
+    <t xml:space="preserve">4.59773397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245943069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300947189331</t>
+    <t xml:space="preserve">4.59300899505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
+    <t xml:space="preserve">4.73476934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56465768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.56465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
+    <t xml:space="preserve">4.03542184829712</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091534614563</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036554336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926689147949</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.53157949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.75366973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
+    <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718852996826</t>
+    <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400470733643</t>
+    <t xml:space="preserve">5.04663991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783398628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321654319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">3.7140998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -35059,7 +35059,7 @@
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
-        <v>46029.6747453704</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B1259" t="n">
         <v>9881</v>
@@ -35080,6 +35080,32 @@
         <v>664</v>
       </c>
       <c r="H1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="1" t="n">
+        <v>46030.3412731482</v>
+      </c>
+      <c r="B1260" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1260" t="s">
+        <v>664</v>
+      </c>
+      <c r="H1260" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
+    <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -125,58 +125,58 @@
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29985117912292</t>
+    <t xml:space="preserve">3.17763471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76051449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80752086639404</t>
+    <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710043907166</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68530440330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304004669189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">7.86292886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.73062038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -689,31 +689,31 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,34 +839,34 @@
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.59773445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.48905181884766</t>
@@ -908,52 +908,52 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.42762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
+    <t xml:space="preserve">4.92378091812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.3360743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486404418945</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35085,7 +35085,7 @@
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
-        <v>46030.3412731482</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B1260" t="n">
         <v>1000</v>
@@ -35106,6 +35106,32 @@
         <v>664</v>
       </c>
       <c r="H1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="1" t="n">
+        <v>46031.4905787037</v>
+      </c>
+      <c r="B1261" t="n">
+        <v>5240</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>663</v>
+      </c>
+      <c r="H1261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="667">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7451753616333</t>
+    <t xml:space="preserve">2.71697187423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453722000122</t>
+    <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650128364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428458213806</t>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590260505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
+    <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632327079773</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.62889623641968</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014270782471</t>
+    <t xml:space="preserve">3.63849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
+    <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.76135325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
+    <t xml:space="preserve">5.50027084350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.65148067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
+    <t xml:space="preserve">7.57941007614136</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347114562988</t>
+    <t xml:space="preserve">6.97456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347066879272</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216613769531</t>
+    <t xml:space="preserve">7.80622625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -365,82 +365,82 @@
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326431274414</t>
+    <t xml:space="preserve">8.31655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523878097534</t>
+    <t xml:space="preserve">7.99523830413818</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698993682861</t>
+    <t xml:space="preserve">7.61721277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270650863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039754867554</t>
+    <t xml:space="preserve">6.65324735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039707183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35082769393921</t>
+    <t xml:space="preserve">6.44533443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.73830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03895664215088</t>
+    <t xml:space="preserve">5.78378963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.97280263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467273712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.28467321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577234268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.00115346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
+    <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
+    <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">6.02950572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">5.94445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.07675933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125736236572</t>
+    <t xml:space="preserve">5.53807258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125783920288</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -812,40 +812,40 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7205924987793</t>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47960186004639</t>
+    <t xml:space="preserve">4.45124912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257204055786</t>
+    <t xml:space="preserve">4.63081169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883262634277</t>
+    <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
+    <t xml:space="preserve">4.60245943069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.73476934432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
+    <t xml:space="preserve">4.55520677566528</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.48905181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036554336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
+    <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.42762327194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75366973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
+    <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.3266236782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.14706182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">3.7140998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
+    <t xml:space="preserve">3.02420353889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
+    <t xml:space="preserve">3.01475286483765</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2010,6 +2010,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.03999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949999988079071</t>
   </si>
 </sst>
 </file>
@@ -35134,7 +35137,7 @@
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
-        <v>46034.5191203704</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B1262" t="n">
         <v>8911</v>
@@ -35155,6 +35158,32 @@
         <v>660</v>
       </c>
       <c r="H1262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="n">
+        <v>46035.6912615741</v>
+      </c>
+      <c r="B1263" t="n">
+        <v>2642</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>666</v>
+      </c>
+      <c r="H1263" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="668">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
+    <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.61949467658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254819393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.77931666374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.76991581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2013,6 +2013,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.949999988079071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990000009536743</t>
   </si>
 </sst>
 </file>
@@ -35163,7 +35166,7 @@
     </row>
     <row r="1263">
       <c r="A1263" s="1" t="n">
-        <v>46035.6912615741</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B1263" t="n">
         <v>2642</v>
@@ -35184,6 +35187,32 @@
         <v>666</v>
       </c>
       <c r="H1263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="n">
+        <v>46036.69125</v>
+      </c>
+      <c r="B1264" t="n">
+        <v>10936</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>667</v>
+      </c>
+      <c r="H1264" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.54428505897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242462158203</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344348907471</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -35192,7 +35192,7 @@
     </row>
     <row r="1264">
       <c r="A1264" s="1" t="n">
-        <v>46036.69125</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B1264" t="n">
         <v>10936</v>
@@ -35213,6 +35213,32 @@
         <v>667</v>
       </c>
       <c r="H1264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>46037.6910763889</v>
+      </c>
+      <c r="B1265" t="n">
+        <v>24931</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>661</v>
+      </c>
+      <c r="H1265" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="669">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590284347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009359359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.67590260505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009335517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.19643759727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164769172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632374763489</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350765228271</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">3.85585927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565292358398</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5002703666687</t>
+    <t xml:space="preserve">5.50027084350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171903610229</t>
+    <t xml:space="preserve">7.6928186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171855926514</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
+    <t xml:space="preserve">8.39216423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.957435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.76665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039754867554</t>
+    <t xml:space="preserve">7.39039707183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489557266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15236473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577234268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1523642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.70818376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.29412364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
+    <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.45124912261963</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245990753174</t>
+    <t xml:space="preserve">4.60245943069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476886749268</t>
+    <t xml:space="preserve">4.73476934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.48905181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036554336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
+    <t xml:space="preserve">3.93146443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9220142364502</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.53157949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75366973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321630477905</t>
+    <t xml:space="preserve">3.21321654319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2016,6 +2016,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.990000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970000028610229</t>
   </si>
 </sst>
 </file>
@@ -35218,7 +35221,7 @@
     </row>
     <row r="1265">
       <c r="A1265" s="1" t="n">
-        <v>46037.6910763889</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B1265" t="n">
         <v>24931</v>
@@ -35239,6 +35242,32 @@
         <v>661</v>
       </c>
       <c r="H1265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="n">
+        <v>46038.6910763889</v>
+      </c>
+      <c r="B1266" t="n">
+        <v>5560</v>
+      </c>
+      <c r="C1266" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>668</v>
+      </c>
+      <c r="H1266" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="670">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009335517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.67590284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61949467658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
+    <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643759727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632374763489</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.76991581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.6853039264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2019,6 +2019,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.970000028610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930000007152557</t>
   </si>
 </sst>
 </file>
@@ -35247,7 +35250,7 @@
     </row>
     <row r="1266">
       <c r="A1266" s="1" t="n">
-        <v>46038.6910763889</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B1266" t="n">
         <v>5560</v>
@@ -35268,6 +35271,32 @@
         <v>668</v>
       </c>
       <c r="H1266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="n">
+        <v>46041.6910069444</v>
+      </c>
+      <c r="B1267" t="n">
+        <v>32758</v>
+      </c>
+      <c r="C1267" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>0.984000027179718</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>669</v>
+      </c>
+      <c r="H1267" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="671">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453722000122</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52548217773438</t>
+    <t xml:space="preserve">3.5254819393158</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242462158203</t>
+    <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344348907471</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
+    <t xml:space="preserve">3.92973756790161</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -2022,6 +2022,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.930000007152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952000021934509</t>
   </si>
 </sst>
 </file>
@@ -35276,7 +35279,7 @@
     </row>
     <row r="1267">
       <c r="A1267" s="1" t="n">
-        <v>46041.6910069444</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B1267" t="n">
         <v>32758</v>
@@ -35285,7 +35288,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="D1267" t="n">
-        <v>0.935999989509583</v>
+        <v>0.930000007152557</v>
       </c>
       <c r="E1267" t="n">
         <v>0.984000027179718</v>
@@ -35297,6 +35300,32 @@
         <v>669</v>
       </c>
       <c r="H1267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="n">
+        <v>46042.6846643519</v>
+      </c>
+      <c r="B1268" t="n">
+        <v>7729</v>
+      </c>
+      <c r="C1268" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>0.941999971866608</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>0.941999971866608</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="G1268" t="s">
+        <v>670</v>
+      </c>
+      <c r="H1268" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="672">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
+    <t xml:space="preserve">2.82085561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.31912398338318</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -86,37 +86,37 @@
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625886917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206811904907</t>
+    <t xml:space="preserve">3.42206835746765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242438316345</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308722496033</t>
+    <t xml:space="preserve">3.71350789070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308746337891</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69470524787903</t>
+    <t xml:space="preserve">3.73231029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.51563692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565292358398</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
+    <t xml:space="preserve">7.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
+    <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">7.9385347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76842355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.76842260360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709287643433</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
+    <t xml:space="preserve">5.80269002914429</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15236473083496</t>
+    <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.32247591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.53807258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
+    <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.70641660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
+    <t xml:space="preserve">4.53630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
+    <t xml:space="preserve">4.77257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663579940796</t>
+    <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.62136077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
+    <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90311312675476</t>
+    <t xml:space="preserve">3.90311288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926736831665</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740455627441</t>
+    <t xml:space="preserve">4.46542596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.32839107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.24333524703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2025,6 +2025,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.952000021934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977999985218048</t>
   </si>
 </sst>
 </file>
@@ -35305,7 +35308,7 @@
     </row>
     <row r="1268">
       <c r="A1268" s="1" t="n">
-        <v>46042.6846643519</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B1268" t="n">
         <v>7729</v>
@@ -35326,6 +35329,32 @@
         <v>670</v>
       </c>
       <c r="H1268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="1" t="n">
+        <v>46043.5475231481</v>
+      </c>
+      <c r="B1269" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C1269" t="n">
+        <v>0.987999975681305</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>0.944000005722046</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>0.96399998664856</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>0.977999985218048</v>
+      </c>
+      <c r="G1269" t="s">
+        <v>671</v>
+      </c>
+      <c r="H1269" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="673">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650128364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428458213806</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206835746765</t>
+    <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284504890442</t>
+    <t xml:space="preserve">3.41266679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164745330811</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632327079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,46 +176,46 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
+    <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.69470524787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.51563668251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697441101074</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402799606323</t>
+    <t xml:space="preserve">7.84402894973755</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">7.80622577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.22205352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">6.76665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.35082769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
+    <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654378890991</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
+    <t xml:space="preserve">6.28467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.59477663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
+    <t xml:space="preserve">6.29412317276001</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817283630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.47960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39454555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.62136125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311288833618</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.32839155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.27168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.32662391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
+    <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2028,6 +2028,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.977999985218048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962000012397766</t>
   </si>
 </sst>
 </file>
@@ -35334,7 +35337,7 @@
     </row>
     <row r="1269">
       <c r="A1269" s="1" t="n">
-        <v>46043.5475231481</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B1269" t="n">
         <v>1294</v>
@@ -35355,6 +35358,32 @@
         <v>671</v>
       </c>
       <c r="H1269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="1" t="n">
+        <v>46044.6834143518</v>
+      </c>
+      <c r="B1270" t="n">
+        <v>5343</v>
+      </c>
+      <c r="C1270" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>0.962000012397766</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>0.962000012397766</v>
+      </c>
+      <c r="G1270" t="s">
+        <v>672</v>
+      </c>
+      <c r="H1270" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.82085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">3.31912398338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.90153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428458213806</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009383201599</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
+    <t xml:space="preserve">3.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2246413230896</t>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81692218780518</t>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530440330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69470548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69470524787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
+    <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -242,37 +242,37 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.65148067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -308,28 +308,28 @@
     <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,67 +377,67 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
     <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">8.14644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74952173233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
+    <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.23742008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302499771118</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1523642539978</t>
+    <t xml:space="preserve">6.15236473083496</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
+    <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">5.94445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5758752822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.56642484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57587575912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125736236572</t>
+    <t xml:space="preserve">5.31125783920288</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.70641708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
+    <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -878,46 +878,46 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47015142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,34 +926,34 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10157632827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12520265579224</t>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10157680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
+    <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
+    <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.88421177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,46 +1085,46 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
+    <t xml:space="preserve">3.32662391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
     <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.7140998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
+    <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.23211765289307</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -35395,7 +35395,7 @@
     </row>
     <row r="1271">
       <c r="A1271" s="1" t="n">
-        <v>46045.6685532407</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B1271" t="n">
         <v>8972</v>
@@ -35416,6 +35416,32 @@
         <v>674</v>
       </c>
       <c r="H1271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="1" t="n">
+        <v>46048.6911111111</v>
+      </c>
+      <c r="B1272" t="n">
+        <v>550</v>
+      </c>
+      <c r="C1272" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G1272" t="s">
+        <v>674</v>
+      </c>
+      <c r="H1272" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085609436035</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153408050537</t>
+    <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009383201599</t>
+    <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52548217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.5254819393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
+    <t xml:space="preserve">3.1964373588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242438316345</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.2998514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973756790161</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62889623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290921211243</t>
+    <t xml:space="preserve">3.6288959980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231077194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -35421,13 +35421,13 @@
     </row>
     <row r="1272">
       <c r="A1272" s="1" t="n">
-        <v>46048.6911111111</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B1272" t="n">
         <v>550</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.953999996185303</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="D1272" t="n">
         <v>0.953999996185303</v>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="675">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,28 +44,28 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650128364563</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548241615295</t>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
+    <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92973685264587</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.76051425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62889623641968</t>
+    <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231029510498</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014270782471</t>
+    <t xml:space="preserve">3.63849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.76135325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488828659058</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.55697393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347114562988</t>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347066879272</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -344,82 +344,82 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216613769531</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326431274414</t>
+    <t xml:space="preserve">8.22205257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
+    <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">8.60007858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698993682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.52270650863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698945999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.18248319625854</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
+    <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
+    <t xml:space="preserve">6.51148843765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.35082721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895664215088</t>
+    <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.13346242904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467273712158</t>
+    <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,28 +671,28 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
+    <t xml:space="preserve">5.79324054718018</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.81037378311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47960186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257204055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47960138320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465721130371</t>
+    <t xml:space="preserve">4.62608623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465768814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60718488693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.60718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,37 +923,37 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.09389305114746</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
+    <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663991928101</t>
+    <t xml:space="preserve">5.03718852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993635177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663944244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1061,34 +1061,34 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32662391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.24156808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3266236782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
+    <t xml:space="preserve">3.02420353889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2034,6 +2034,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.980000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966000020503998</t>
   </si>
 </sst>
 </file>
@@ -35470,7 +35473,7 @@
     </row>
     <row r="1274">
       <c r="A1274" s="1" t="n">
-        <v>46050.6786226852</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B1274" t="n">
         <v>10613</v>
@@ -35491,6 +35494,32 @@
         <v>673</v>
       </c>
       <c r="H1274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="1" t="n">
+        <v>46051.6804861111</v>
+      </c>
+      <c r="B1275" t="n">
+        <v>4520</v>
+      </c>
+      <c r="C1275" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="G1275" t="s">
+        <v>674</v>
+      </c>
+      <c r="H1275" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="677">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2040,6 +2040,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.966000020503998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973999977111816</t>
   </si>
 </sst>
 </file>
@@ -35528,7 +35531,7 @@
     </row>
     <row r="1276">
       <c r="A1276" s="1" t="n">
-        <v>46052.6111458333</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B1276" t="n">
         <v>5410</v>
@@ -35549,6 +35552,32 @@
         <v>675</v>
       </c>
       <c r="H1276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>46055.6169212963</v>
+      </c>
+      <c r="B1277" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1277" t="n">
+        <v>0.973999977111816</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>0.973999977111816</v>
+      </c>
+      <c r="G1277" t="s">
+        <v>676</v>
+      </c>
+      <c r="H1277" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="680">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
+    <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -74,64 +74,64 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61009359359741</t>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625863075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326523780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763495445251</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752086639404</t>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350789070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710043907166</t>
+    <t xml:space="preserve">3.71350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.67629742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.29235649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
+    <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
     <t xml:space="preserve">7.93853378295898</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.39039754867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.51148843765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
+    <t xml:space="preserve">6.13346242904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
+    <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
     <t xml:space="preserve">6.34137678146362</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466497421265</t>
+    <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.07675838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.79324054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.59773445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56465721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.56465768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091534614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.96926689147949</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.75367069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
+    <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718900680542</t>
+    <t xml:space="preserve">5.03718852996826</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.04663944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21321654319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24156832695007</t>
+    <t xml:space="preserve">3.77080368995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21321630477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24156808853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -2049,6 +2049,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.958000004291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959999978542328</t>
   </si>
 </sst>
 </file>
@@ -35615,7 +35618,7 @@
     </row>
     <row r="1279">
       <c r="A1279" s="1" t="n">
-        <v>46057.512662037</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B1279" t="n">
         <v>5327</v>
@@ -35636,6 +35639,32 @@
         <v>678</v>
       </c>
       <c r="H1279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>46058.5104050926</v>
+      </c>
+      <c r="B1280" t="n">
+        <v>4046</v>
+      </c>
+      <c r="C1280" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>0.941999971866608</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>0.958000004291534</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G1280" t="s">
+        <v>679</v>
+      </c>
+      <c r="H1280" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="681">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.35625886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667953491211</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.46907424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
+    <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">3.80752062797546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871870040894</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350812911987</t>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.67629766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585951805115</t>
+    <t xml:space="preserve">3.85585975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706958770752</t>
+    <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488733291626</t>
+    <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">7.99523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">8.07084274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
+    <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
     <t xml:space="preserve">7.76842308044434</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.51148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.13346290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654426574707</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37917947769165</t>
+    <t xml:space="preserve">6.64379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37917900085449</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">6.34137678146362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038202285767</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005529403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
+    <t xml:space="preserve">6.02005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324054718018</t>
+    <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
+    <t xml:space="preserve">5.43411540985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
+    <t xml:space="preserve">4.67333984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.7725715637207</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795316696167</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
+    <t xml:space="preserve">4.62608671188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.9031126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993635177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663944244385</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993587493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
+    <t xml:space="preserve">4.93323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927513122559</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79915571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77080368995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47783422470093</t>
+    <t xml:space="preserve">3.79915547370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77080392837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47783398628235</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360743522644</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
+    <t xml:space="preserve">3.87476062774658</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2052,6 +2052,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.959999978542328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955999970436096</t>
   </si>
 </sst>
 </file>
@@ -35644,7 +35647,7 @@
     </row>
     <row r="1280">
       <c r="A1280" s="1" t="n">
-        <v>46058.5104050926</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B1280" t="n">
         <v>4046</v>
@@ -35665,6 +35668,32 @@
         <v>679</v>
       </c>
       <c r="H1280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>46059.6613773148</v>
+      </c>
+      <c r="B1281" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C1281" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>0.955999970436096</v>
+      </c>
+      <c r="G1281" t="s">
+        <v>680</v>
+      </c>
+      <c r="H1281" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650128364563</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52548241615295</t>
+    <t xml:space="preserve">3.57248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
+    <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92973685264587</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7605140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.76051425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">3.65710020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62889623641968</t>
+    <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231029510498</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014270782471</t>
+    <t xml:space="preserve">3.63849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.76135325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488828659058</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.55697393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456979751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347114562988</t>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347066879272</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -344,82 +344,82 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216613769531</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326431274414</t>
+    <t xml:space="preserve">8.22205257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
+    <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
+    <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
+    <t xml:space="preserve">7.86292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
     <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
+    <t xml:space="preserve">8.60007858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698993682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.52270650863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698945999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324783325195</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
     <t xml:space="preserve">7.18248319625854</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
+    <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
+    <t xml:space="preserve">6.51148843765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.35082721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">6.58709287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895664215088</t>
+    <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.13346242904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467273712158</t>
+    <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577138900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,28 +671,28 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.14291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.72708511352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
+    <t xml:space="preserve">5.79324054718018</t>
   </si>
   <si>
     <t xml:space="preserve">5.56642436981201</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7158670425415</t>
+    <t xml:space="preserve">4.81037378311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71586751937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47960186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257204055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.72059297561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47960138320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465721130371</t>
+    <t xml:space="preserve">4.62608623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465768814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60718488693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.60718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -923,37 +923,37 @@
     <t xml:space="preserve">4.08739995956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509099960327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.09389305114746</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
+    <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98993587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04663991928101</t>
+    <t xml:space="preserve">5.03718852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98993635177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04663944244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.26400470733643</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168798446655</t>
+    <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
     <t xml:space="preserve">4.24333572387695</t>
@@ -1061,34 +1061,34 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32662391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.24156808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3266236782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706158638</t>
+    <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
+    <t xml:space="preserve">3.02420353889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35754,7 +35754,7 @@
     </row>
     <row r="1284">
       <c r="A1284" s="1" t="n">
-        <v>46064.6631944444</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B1284" t="n">
         <v>10260</v>
@@ -35775,6 +35775,32 @@
         <v>681</v>
       </c>
       <c r="H1284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>46065.652349537</v>
+      </c>
+      <c r="B1285" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1285" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G1285" t="s">
+        <v>666</v>
+      </c>
+      <c r="H1285" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.59129095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428505897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949491500854</t>
+    <t xml:space="preserve">3.61949467658997</t>
   </si>
   <si>
     <t xml:space="preserve">3.57248854637146</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266703605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284504890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19643712043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.46907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6006920337677</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
     <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632374763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290921211243</t>
+    <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
     <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629742622375</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
+    <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148019790649</t>
+    <t xml:space="preserve">5.65148067474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402799606323</t>
+    <t xml:space="preserve">7.84402894973755</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
     <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29765796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.29765892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292839050293</t>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -407,34 +407,34 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062038421631</t>
+    <t xml:space="preserve">7.42819976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951349258423</t>
+    <t xml:space="preserve">7.34314441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951396942139</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95566844940186</t>
+    <t xml:space="preserve">6.9556679725647</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.51148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533395767212</t>
+    <t xml:space="preserve">6.44533443450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830366134644</t>
+    <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378915786743</t>
+    <t xml:space="preserve">5.78378963470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280216217041</t>
+    <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
+    <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.21851825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577138900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
+    <t xml:space="preserve">6.22796964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
+    <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
     <t xml:space="preserve">6.50203800201416</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.42466497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">6.02950572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
+    <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
+    <t xml:space="preserve">5.94445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
+    <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
+    <t xml:space="preserve">6.12401247024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.79324007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71586751937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70641660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531795501709</t>
+    <t xml:space="preserve">4.81037425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7158670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70641708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531843185425</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.53630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.50795364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56465768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.56465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
+    <t xml:space="preserve">4.03542184829712</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -926,40 +926,40 @@
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.90311312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509123802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367069244385</t>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.09389305114746</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
+    <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718852996826</t>
+    <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400470733643</t>
+    <t xml:space="preserve">5.04663991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783398628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.24156832695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1659631729126</t>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16596293449402</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432319641113</t>
+    <t xml:space="preserve">3.7140998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432271957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35780,7 +35780,7 @@
     </row>
     <row r="1285">
       <c r="A1285" s="1" t="n">
-        <v>46065.652349537</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B1285" t="n">
         <v>2500</v>
@@ -35801,6 +35801,32 @@
         <v>666</v>
       </c>
       <c r="H1285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>46066.555625</v>
+      </c>
+      <c r="B1286" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C1286" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G1286" t="s">
+        <v>678</v>
+      </c>
+      <c r="H1286" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
+    <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
     <t xml:space="preserve">3.3191237449646</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">3.63453722000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.90153384208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
+    <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129095077515</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949467658997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -98,34 +98,34 @@
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326547622681</t>
+    <t xml:space="preserve">3.40326523780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206835746765</t>
+    <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
+    <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643712043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.1964373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242462158203</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608109474182</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.81692171096802</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931690216064</t>
+    <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632374763489</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
+    <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">3.72290897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
+    <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67629766464233</t>
+    <t xml:space="preserve">3.48728489875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67629742622375</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.59124183654785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565292358398</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">7.57941055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.80622625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29765796661377</t>
+    <t xml:space="preserve">8.392165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205352783203</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523830413818</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062086105347</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.76665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824836730957</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939407348633</t>
+    <t xml:space="preserve">5.85939455032349</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.97280263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23741960525513</t>
+    <t xml:space="preserve">6.23742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">6.22796964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1523642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15236473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">6.14291334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.502037525177</t>
+    <t xml:space="preserve">6.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.86884546279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">6.32247543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">6.07675933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5758752822876</t>
+    <t xml:space="preserve">5.57587575912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125783920288</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70641660690308</t>
+    <t xml:space="preserve">4.70641708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.70169115066528</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663627624512</t>
+    <t xml:space="preserve">4.61663579940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
+    <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.62608623504639</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311312675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509123802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157632827759</t>
+    <t xml:space="preserve">4.10157680511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179504394531</t>
+    <t xml:space="preserve">4.01179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080392837524</t>
+    <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783398628235</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11870980262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11871004104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596293449402</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55343914031982</t>
+    <t xml:space="preserve">3.61959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5534393787384</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969703674316</t>
+    <t xml:space="preserve">3.02420377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35893,7 +35893,7 @@
     </row>
     <row r="1289">
       <c r="A1289" s="1" t="n">
-        <v>46071.6912731481</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B1289" t="n">
         <v>2230</v>
@@ -35914,6 +35914,32 @@
         <v>684</v>
       </c>
       <c r="H1289" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="1" t="n">
+        <v>46072.6912962963</v>
+      </c>
+      <c r="B1290" t="n">
+        <v>7086</v>
+      </c>
+      <c r="C1290" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G1290" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1290" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
+    <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033648490906</t>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
+    <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57248854637146</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41266679763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.46907448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284504890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
+    <t xml:space="preserve">3.22464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608109474182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60069227218628</t>
+    <t xml:space="preserve">3.45027184486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6006920337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.92973709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">3.77931666374207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71350765228271</t>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728489875793</t>
+    <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629742622375</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
+    <t xml:space="preserve">3.59124159812927</t>
   </si>
   <si>
     <t xml:space="preserve">3.6290442943573</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">4.49850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235601425171</t>
+    <t xml:space="preserve">5.29235649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20138454437256</t>
+    <t xml:space="preserve">7.2013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
+    <t xml:space="preserve">7.88183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402894973755</t>
+    <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.54160737991333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456979751587</t>
+    <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347066879272</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732442855835</t>
+    <t xml:space="preserve">7.78732395172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622625350952</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
   </si>
   <si>
     <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.29765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
+    <t xml:space="preserve">7.86292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -407,34 +407,34 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42819976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.42820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512664794922</t>
+    <t xml:space="preserve">7.82512617111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
+    <t xml:space="preserve">6.65324735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">6.98401975631714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.51148843765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
+    <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709287643433</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939455032349</t>
+    <t xml:space="preserve">5.85939407348633</t>
   </si>
   <si>
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
+    <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774633407593</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346290588379</t>
+    <t xml:space="preserve">6.13346242904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47368574142456</t>
+    <t xml:space="preserve">6.4736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23742008209229</t>
+    <t xml:space="preserve">6.21851873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.36027812957764</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15236473083496</t>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577138900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840755462646</t>
+    <t xml:space="preserve">6.04840707778931</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291334152222</t>
+    <t xml:space="preserve">6.14291381835938</t>
   </si>
   <si>
     <t xml:space="preserve">6.50203800201416</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653650283813</t>
+    <t xml:space="preserve">5.73653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708559036255</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
     <t xml:space="preserve">5.8499436378479</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
+    <t xml:space="preserve">5.75543737411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.7459864616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86884546279907</t>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412317276001</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
+    <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57587575912476</t>
+    <t xml:space="preserve">5.79324054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.43411588668823</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.53807258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7158670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.81037378311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71586751937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70641660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124959945679</t>
+    <t xml:space="preserve">4.53630495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45125007629395</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">4.7725715637207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54575634002686</t>
+    <t xml:space="preserve">4.5457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795364379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.50795316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191082000732</t>
+    <t xml:space="preserve">4.61191034317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">4.62608623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56465721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47015142440796</t>
+    <t xml:space="preserve">4.56465768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136125564575</t>
+    <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
+    <t xml:space="preserve">4.03542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -926,40 +926,40 @@
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10157680511475</t>
+    <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.51740407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.09389305114746</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
+    <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03718900680542</t>
+    <t xml:space="preserve">5.03718852996826</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.04663944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839155197144</t>
+    <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01179456710815</t>
+    <t xml:space="preserve">4.01179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421177864075</t>
+    <t xml:space="preserve">3.88421154022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">3.77080368995667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156832695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32662391662598</t>
+    <t xml:space="preserve">3.24156808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15651249885559</t>
+    <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11871004104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14706158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.11870980262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14706182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">3.71410012245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.26046967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420377731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92969727516174</t>
+    <t xml:space="preserve">3.02420353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92969703674316</t>
   </si>
   <si>
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35919,13 +35919,13 @@
     </row>
     <row r="1290">
       <c r="A1290" s="1" t="n">
-        <v>46072.6912962963</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B1290" t="n">
         <v>7086</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.935999989509583</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="D1290" t="n">
         <v>0.935999989509583</v>
@@ -35940,6 +35940,32 @@
         <v>683</v>
       </c>
       <c r="H1290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="1" t="n">
+        <v>46073.6911805556</v>
+      </c>
+      <c r="B1291" t="n">
+        <v>5612</v>
+      </c>
+      <c r="C1291" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G1291" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1291" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410656929016</t>
+    <t xml:space="preserve">3.9203360080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248878479004</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40326523780823</t>
+    <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.50667977333069</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284504890442</t>
+    <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164721488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22464084625244</t>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
+    <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6006920337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92973709106445</t>
+    <t xml:space="preserve">3.60069227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">3.76051425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931666374207</t>
+    <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
     <t xml:space="preserve">3.82632350921631</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991581916809</t>
+    <t xml:space="preserve">3.78871822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67629742622375</t>
+    <t xml:space="preserve">3.67629766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.58179092407227</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
+    <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.04487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235649108887</t>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.5002703666687</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">7.16358184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2013840675354</t>
+    <t xml:space="preserve">7.20138454437256</t>
   </si>
   <si>
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
     <t xml:space="preserve">7.69281816482544</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54160737991333</t>
+    <t xml:space="preserve">7.57941007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">7.95743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413917541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292839050293</t>
+    <t xml:space="preserve">8.01413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073156356812</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">7.44710159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43765068054199</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
+    <t xml:space="preserve">6.9840202331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.95566844940186</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51148843765259</t>
+    <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
     <t xml:space="preserve">6.3319263458252</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
+    <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
     <t xml:space="preserve">6.62489604949951</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13346242904663</t>
+    <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.64379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478439331055</t>
+    <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851873397827</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.34137630462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577138900757</t>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">6.01060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50203800201416</t>
+    <t xml:space="preserve">6.14291334152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.502037525177</t>
   </si>
   <si>
     <t xml:space="preserve">6.72885274887085</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">5.774338722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.547523021698</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005529403687</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">6.06730890274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">4.81037378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71586751937866</t>
+    <t xml:space="preserve">4.7158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70641660690308</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45125007629395</t>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">4.67333936691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56465768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.62608575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
+    <t xml:space="preserve">4.03542184829712</t>
   </si>
   <si>
     <t xml:space="preserve">4.02597141265869</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
+    <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.95036578178406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146419525146</t>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09389305114746</t>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">4.88597869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03718852996826</t>
+    <t xml:space="preserve">4.9521336555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04663944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.04663991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77080368995667</t>
+    <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
     <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24156808853149</t>
+    <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.3266236782074</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5534393787384</t>
+    <t xml:space="preserve">3.61959338188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55343914031982</t>
   </si>
   <si>
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -35945,7 +35945,7 @@
     </row>
     <row r="1291">
       <c r="A1291" s="1" t="n">
-        <v>46073.6911805556</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B1291" t="n">
         <v>5612</v>
@@ -35966,6 +35966,32 @@
         <v>683</v>
       </c>
       <c r="H1291" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="1" t="n">
+        <v>46076.6106712963</v>
+      </c>
+      <c r="B1292" t="n">
+        <v>968</v>
+      </c>
+      <c r="C1292" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>0.912000000476837</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="G1292" t="s">
+        <v>684</v>
+      </c>
+      <c r="H1292" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">3.9203360080719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66650176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
+    <t xml:space="preserve">3.66650152206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590308189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248878479004</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42206811904907</t>
+    <t xml:space="preserve">3.42206835746765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763447761536</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027208328247</t>
+    <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.51608085632324</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.78871846199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62889623641968</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
+    <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -374,58 +374,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,52 +443,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379692077637</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,91 +875,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.3945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -989,43 +989,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.93323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.88421154022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.47783398628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -35971,7 +35971,7 @@
     </row>
     <row r="1292">
       <c r="A1292" s="1" t="n">
-        <v>46076.6106712963</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B1292" t="n">
         <v>968</v>
@@ -35992,6 +35992,32 @@
         <v>684</v>
       </c>
       <c r="H1292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="1" t="n">
+        <v>46077.6709606481</v>
+      </c>
+      <c r="B1293" t="n">
+        <v>5580</v>
+      </c>
+      <c r="C1293" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>0.935999989509583</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G1293" t="s">
+        <v>683</v>
+      </c>
+      <c r="H1293" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="686">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912422180176</t>
   </si>
   <si>
     <t xml:space="preserve">3.63453698158264</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
+    <t xml:space="preserve">3.92033576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590308189392</t>
+    <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42206835746765</t>
+    <t xml:space="preserve">3.50667953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
     <t xml:space="preserve">3.46907448768616</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242414474487</t>
+    <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.27164769172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763447761536</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608061790466</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350789070129</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350812911987</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -374,58 +374,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,52 +443,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.37917947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.43411588668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
+    <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,91 +875,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -989,43 +989,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421130180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.87476086616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2067,6 +2067,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.935999989509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934000015258789</t>
   </si>
 </sst>
 </file>
@@ -35997,7 +36000,7 @@
     </row>
     <row r="1293">
       <c r="A1293" s="1" t="n">
-        <v>46077.6709606481</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B1293" t="n">
         <v>5580</v>
@@ -36018,6 +36021,32 @@
         <v>683</v>
       </c>
       <c r="H1293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="1" t="n">
+        <v>46078.6612847222</v>
+      </c>
+      <c r="B1294" t="n">
+        <v>10376</v>
+      </c>
+      <c r="C1294" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="G1294" t="s">
+        <v>685</v>
+      </c>
+      <c r="H1294" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="687">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,22 +50,22 @@
     <t xml:space="preserve">2.71697163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912422180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650128364563</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428482055664</t>
+    <t xml:space="preserve">3.59129118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428458213806</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248854637146</t>
+    <t xml:space="preserve">3.57248830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41266703605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25284504890442</t>
+    <t xml:space="preserve">3.41266679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
+    <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608061790466</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973756790161</t>
+    <t xml:space="preserve">3.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
@@ -161,61 +161,61 @@
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632350921631</t>
+    <t xml:space="preserve">3.82632327079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78871846199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350812911987</t>
+    <t xml:space="preserve">3.78871822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76991581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853039264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231053352356</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.51563668251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
+    <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12992811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49850273132324</t>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4985032081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.55697441101074</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84402799606323</t>
+    <t xml:space="preserve">7.84402894973755</t>
   </si>
   <si>
     <t xml:space="preserve">7.71171903610229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
+    <t xml:space="preserve">6.97456979751587</t>
   </si>
   <si>
     <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">7.80622577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.22205352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
+    <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
     <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91963338851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01413822174072</t>
+    <t xml:space="preserve">7.91963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01413917541504</t>
   </si>
   <si>
     <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">6.76665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11456108093262</t>
+    <t xml:space="preserve">6.35082769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
+    <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.99170351028442</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
+    <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
     <t xml:space="preserve">6.59654378890991</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
+    <t xml:space="preserve">6.28467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.59477663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
+    <t xml:space="preserve">6.29412317276001</t>
   </si>
   <si>
     <t xml:space="preserve">6.18071603775024</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.02005529403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.7205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41817283630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.47960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62136077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39454555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.62136125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90311288833618</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92201399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
   </si>
   <si>
     <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.32839155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.27168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
+    <t xml:space="preserve">3.88421177864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
+    <t xml:space="preserve">3.32662391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.18486428260803</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706182479858</t>
+    <t xml:space="preserve">3.14706158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.1659631729126</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
+    <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2070,6 +2070,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.934000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927999973297119</t>
   </si>
 </sst>
 </file>
@@ -36026,7 +36029,7 @@
     </row>
     <row r="1294">
       <c r="A1294" s="1" t="n">
-        <v>46078.6612847222</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B1294" t="n">
         <v>10376</v>
@@ -36047,6 +36050,32 @@
         <v>685</v>
       </c>
       <c r="H1294" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="1" t="n">
+        <v>46079.6203819444</v>
+      </c>
+      <c r="B1295" t="n">
+        <v>4290</v>
+      </c>
+      <c r="C1295" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="G1295" t="s">
+        <v>686</v>
+      </c>
+      <c r="H1295" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,25 +47,25 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7451753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74517560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31912422180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.90153360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92033648490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650152206421</t>
+    <t xml:space="preserve">3.92033576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650176048279</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428505897522</t>
+    <t xml:space="preserve">3.55368590354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949467658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.61949491500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42206835746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46907472610474</t>
+    <t xml:space="preserve">3.50667953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42206811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46907448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266703605652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284481048584</t>
+    <t xml:space="preserve">3.25284504890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19643712043762</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344348907471</t>
+    <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164769172668</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.17763495445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608061790466</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,31 +170,31 @@
     <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991581916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56308746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65710020065308</t>
+    <t xml:space="preserve">3.76991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56308722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65710043907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.6288959980011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72290897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68530416488647</t>
+    <t xml:space="preserve">3.72290921211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
     <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69470548629761</t>
+    <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.72355079650879</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.80860638618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585927963257</t>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487228393555</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4985032081604</t>
+    <t xml:space="preserve">4.12992811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.23565244674683</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">5.48136901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46246814727783</t>
+    <t xml:space="preserve">5.5002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46246767044067</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
+    <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.68928289413452</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
+    <t xml:space="preserve">7.80622577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.39216423034668</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">8.12754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
   </si>
   <si>
     <t xml:space="preserve">7.56050872802734</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39039707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34314441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.39039754867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34314393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
+    <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
+    <t xml:space="preserve">6.11456108093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.29589080810547</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
+    <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.58709335327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
+    <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.03895616531372</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
+    <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
     <t xml:space="preserve">5.88774585723877</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">6.52093935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.64379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">6.45478487014771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">6.28467321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137630462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
+    <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">6.04840707778931</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59477663040161</t>
+    <t xml:space="preserve">5.59477710723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.64202976226807</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
+    <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.73653602600098</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32247543334961</t>
+    <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45124912261963</t>
+    <t xml:space="preserve">4.53630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58355855941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59300899505615</t>
+    <t xml:space="preserve">4.60245990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58355808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.61191034317017</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
+    <t xml:space="preserve">4.39454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">4.3425669670105</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">4.08739948272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509147644043</t>
   </si>
   <si>
     <t xml:space="preserve">3.94091510772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96926689147949</t>
+    <t xml:space="preserve">3.96926736831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.06377410888672</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">4.12520217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53157949447632</t>
+    <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.46542596817017</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75366973876953</t>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213317871094</t>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.26400423049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.27168750762939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
+    <t xml:space="preserve">3.88421130180359</t>
   </si>
   <si>
     <t xml:space="preserve">3.79915571212769</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
+    <t xml:space="preserve">3.47783422470093</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21321654319763</t>
+    <t xml:space="preserve">3.21321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24156832695007</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">3.15651226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
+    <t xml:space="preserve">3.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64794540405273</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05432271957397</t>
+    <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476086616516</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -36113,7 +36113,7 @@
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
-        <v>46083.6848263889</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B1297" t="n">
         <v>5434</v>
@@ -36134,6 +36134,32 @@
         <v>688</v>
       </c>
       <c r="H1297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="1" t="n">
+        <v>46084.6079861111</v>
+      </c>
+      <c r="B1298" t="n">
+        <v>18605</v>
+      </c>
+      <c r="C1298" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="G1298" t="s">
+        <v>687</v>
+      </c>
+      <c r="H1298" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7451753616333</t>
+    <t xml:space="preserve">2.71697187423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74517560005188</t>
   </si>
   <si>
     <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
+    <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
     <t xml:space="preserve">3.67590284347534</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">3.55368614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -86,49 +86,49 @@
     <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.61949515342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25284504890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.25284481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
+    <t xml:space="preserve">3.24344348907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23404240608215</t>
+    <t xml:space="preserve">3.23404216766357</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29985117912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.2998514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76051449775696</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80752062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78871870040894</t>
+    <t xml:space="preserve">3.80752086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78871846199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.76991581916809</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
+    <t xml:space="preserve">3.76135301589966</t>
   </si>
   <si>
     <t xml:space="preserve">3.78025460243225</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488828659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.97456979751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
+    <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
     <t xml:space="preserve">7.95743608474731</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073204040527</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084274291992</t>
+    <t xml:space="preserve">8.60007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
     <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.74952173233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.18248319625854</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
     <t xml:space="preserve">6.61544561386108</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28467321395874</t>
+    <t xml:space="preserve">6.36027812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302499771118</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.84994411468506</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -824,40 +824,40 @@
     <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
+    <t xml:space="preserve">4.63081216812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.67333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257204055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.60718488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47015142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509099960327</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
+    <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
+    <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
     <t xml:space="preserve">4.27168798446655</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772280693054</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.14706158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
+    <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
+    <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -36168,7 +36168,7 @@
     </row>
     <row r="1299">
       <c r="A1299" s="1" t="n">
-        <v>46085.6525115741</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B1299" t="n">
         <v>5293</v>
@@ -36189,6 +36189,32 @@
         <v>687</v>
       </c>
       <c r="H1299" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46086.6864699074</v>
+      </c>
+      <c r="B1300" t="n">
+        <v>4639</v>
+      </c>
+      <c r="C1300" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>0.882000029087067</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>0.906000018119812</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>687</v>
+      </c>
+      <c r="H1300" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="691">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2082,6 +2082,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.892000019550323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896000027656555</t>
   </si>
 </sst>
 </file>
@@ -36194,7 +36197,7 @@
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
-        <v>46086.6864699074</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B1300" t="n">
         <v>4639</v>
@@ -36215,6 +36218,32 @@
         <v>687</v>
       </c>
       <c r="H1300" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46087.6597106481</v>
+      </c>
+      <c r="B1301" t="n">
+        <v>8050</v>
+      </c>
+      <c r="C1301" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>0.882000029087067</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>0.896000027656555</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>690</v>
+      </c>
+      <c r="H1301" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2085,6 +2085,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.896000027656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899999976158142</t>
   </si>
 </sst>
 </file>
@@ -36223,7 +36226,7 @@
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
-        <v>46087.6597106481</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B1301" t="n">
         <v>8050</v>
@@ -36244,6 +36247,32 @@
         <v>690</v>
       </c>
       <c r="H1301" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46090.5181365741</v>
+      </c>
+      <c r="B1302" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1302" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>0.871999979019165</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>691</v>
+      </c>
+      <c r="H1302" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -36252,7 +36252,7 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46090.5181365741</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B1302" t="n">
         <v>10500</v>
@@ -36273,6 +36273,32 @@
         <v>691</v>
       </c>
       <c r="H1302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46091.6453819444</v>
+      </c>
+      <c r="B1303" t="n">
+        <v>619</v>
+      </c>
+      <c r="C1303" t="n">
+        <v>0.916000008583069</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>0.916000008583069</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>691</v>
+      </c>
+      <c r="H1303" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="693">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439867019653</t>
+    <t xml:space="preserve">2.91439843177795</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085585594177</t>
+    <t xml:space="preserve">2.82085561752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -53,31 +53,31 @@
     <t xml:space="preserve">2.7451753616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
+    <t xml:space="preserve">3.31912398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033624649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590308189392</t>
+    <t xml:space="preserve">3.70410680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129118919373</t>
+    <t xml:space="preserve">3.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667977333069</t>
+    <t xml:space="preserve">3.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206835746765</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164721488953</t>
+    <t xml:space="preserve">3.10242438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763447761536</t>
+    <t xml:space="preserve">3.22464084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692171096802</t>
+    <t xml:space="preserve">3.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308722496033</t>
+    <t xml:space="preserve">3.56308746337891</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231053352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69470524787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355055809021</t>
+    <t xml:space="preserve">3.73231029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69470548629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.61014318466187</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563668251038</t>
+    <t xml:space="preserve">3.51563692092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124159812927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6290442943573</t>
+    <t xml:space="preserve">3.59124183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62904405593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025460243225</t>
+    <t xml:space="preserve">3.78025436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487276077271</t>
+    <t xml:space="preserve">3.80860638618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992763519287</t>
+    <t xml:space="preserve">4.12992811203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565196990967</t>
+    <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.48136901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928337097168</t>
+    <t xml:space="preserve">5.68928289413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88183116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
+    <t xml:space="preserve">7.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907606124878</t>
+    <t xml:space="preserve">6.99347114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216423034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205352783203</t>
+    <t xml:space="preserve">8.22205257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -374,58 +374,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963386535645</t>
+    <t xml:space="preserve">8.12754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963338851929</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42820024490356</t>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073156356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42819976806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93853425979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">8.07084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842260360718</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
+    <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721324920654</t>
+    <t xml:space="preserve">7.61721277236938</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,52 +443,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2580885887146</t>
+    <t xml:space="preserve">7.25808811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127336502075</t>
+    <t xml:space="preserve">7.03127384185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6343469619751</t>
+    <t xml:space="preserve">6.46423482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63434648513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665544509888</t>
+    <t xml:space="preserve">6.76665496826172</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18248319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765020370483</t>
+    <t xml:space="preserve">7.1824836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765068054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314441680908</t>
+    <t xml:space="preserve">7.34314393997192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742784500122</t>
+    <t xml:space="preserve">7.09742832183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544561386108</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050144195557</t>
+    <t xml:space="preserve">6.70050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">6.11456108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489652633667</t>
+    <t xml:space="preserve">6.58709335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489604949951</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774633407593</t>
+    <t xml:space="preserve">5.88774585723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.80269002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851825714111</t>
+    <t xml:space="preserve">6.37917947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851873397827</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
+    <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302499771118</t>
+    <t xml:space="preserve">6.34137630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302452087402</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27522230148315</t>
+    <t xml:space="preserve">6.275221824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77433919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54752349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.547523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763515472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
+    <t xml:space="preserve">6.02950620651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84994411468506</t>
+    <t xml:space="preserve">5.8499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94444990158081</t>
+    <t xml:space="preserve">5.94445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
+    <t xml:space="preserve">6.07675886154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730842590332</t>
+    <t xml:space="preserve">6.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730890274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642436981201</t>
+    <t xml:space="preserve">5.56642484664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47191858291626</t>
+    <t xml:space="preserve">5.43411588668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807306289673</t>
+    <t xml:space="preserve">5.53807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19785022735596</t>
+    <t xml:space="preserve">5.1978497505188</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7205924987793</t>
+    <t xml:space="preserve">4.72059297561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817235946655</t>
+    <t xml:space="preserve">4.41817283630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.67333936691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355855941772</t>
+    <t xml:space="preserve">4.58355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,91 +875,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608671188354</t>
+    <t xml:space="preserve">4.62608575820923</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718536376953</t>
+    <t xml:space="preserve">4.55520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34256744384766</t>
+    <t xml:space="preserve">4.39454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3425669670105</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
+    <t xml:space="preserve">4.08739948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036578178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377363204956</t>
+    <t xml:space="preserve">3.95509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487640380859</t>
+    <t xml:space="preserve">4.12520217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487592697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4417986869812</t>
+    <t xml:space="preserve">4.44179916381836</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762279510498</t>
+    <t xml:space="preserve">4.42762327194214</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542549133301</t>
+    <t xml:space="preserve">4.46542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367069244385</t>
+    <t xml:space="preserve">4.75367021560669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -989,43 +989,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9521336555481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993587493896</t>
+    <t xml:space="preserve">4.98993635177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004753112793</t>
+    <t xml:space="preserve">5.26400423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828765869141</t>
+    <t xml:space="preserve">5.01828813552856</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707370758057</t>
+    <t xml:space="preserve">4.43707323074341</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333572387695</t>
+    <t xml:space="preserve">4.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333524703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421130180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772280693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651249885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.30772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71410012245178</t>
+    <t xml:space="preserve">3.7140998840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959362030029</t>
+    <t xml:space="preserve">3.87476086616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959338188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387704849243</t>
+    <t xml:space="preserve">3.37387681007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211765289307</t>
+    <t xml:space="preserve">3.26046967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211741447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200623512268</t>
+    <t xml:space="preserve">3.01475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620059967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95674967765808</t>
+    <t xml:space="preserve">2.9567494392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313654899597</t>
+    <t xml:space="preserve">2.71753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313631057739</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098024368286</t>
+    <t xml:space="preserve">2.64098000526428</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744868278503</t>
+    <t xml:space="preserve">2.49744844436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831106185913</t>
+    <t xml:space="preserve">2.48787975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356785774231</t>
+    <t xml:space="preserve">2.58356761932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56443023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42089867591858</t>
+    <t xml:space="preserve">2.56442999839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4208984375</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79892861843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009441614151</t>
+    <t xml:space="preserve">1.7989284992218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00944137573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6266907453537</t>
+    <t xml:space="preserve">1.62669086456299</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100311756134</t>
+    <t xml:space="preserve">1.53100299835205</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315918445587</t>
+    <t xml:space="preserve">1.48315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410336971283</t>
+    <t xml:space="preserve">1.74630045890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7128096818924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410325050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.679319024086</t>
+    <t xml:space="preserve">1.67931890487671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798443317413</t>
+    <t xml:space="preserve">1.59798431396484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073518276215</t>
+    <t xml:space="preserve">1.98073506355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202887058258</t>
+    <t xml:space="preserve">1.95202875137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866080284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822949409485</t>
+    <t xml:space="preserve">2.24866056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521080970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822925567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124817848206</t>
+    <t xml:space="preserve">2.19124794006348</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642316818237</t>
+    <t xml:space="preserve">2.07642292976379</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391736030579</t>
+    <t xml:space="preserve">2.35391712188721</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693604469299</t>
+    <t xml:space="preserve">2.28693580627441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167948722839</t>
+    <t xml:space="preserve">2.3347795009613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857899665833</t>
+    <t xml:space="preserve">2.02857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771685600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1146981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955605506897</t>
+    <t xml:space="preserve">2.01901006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771661758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11469793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09556031227112</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720362186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763481140137</t>
+    <t xml:space="preserve">1.83720350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763493061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6458283662796</t>
+    <t xml:space="preserve">1.64582824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069439888</t>
+    <t xml:space="preserve">1.87069427967072</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112558841705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9903039932251</t>
+    <t xml:space="preserve">1.86112570762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99030387401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987268447876</t>
+    <t xml:space="preserve">1.99987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2088,6 +2088,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.893999993801117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888000011444092</t>
   </si>
 </sst>
 </file>
@@ -36304,7 +36307,7 @@
     </row>
     <row r="1304">
       <c r="A1304" s="1" t="n">
-        <v>46092.5466203704</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B1304" t="n">
         <v>631</v>
@@ -36325,6 +36328,32 @@
         <v>691</v>
       </c>
       <c r="H1304" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>46093.5377662037</v>
+      </c>
+      <c r="B1305" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C1305" t="n">
+        <v>0.888000011444092</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>0.871999979019165</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>0.888000011444092</v>
+      </c>
+      <c r="G1305" t="s">
+        <v>692</v>
+      </c>
+      <c r="H1305" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91439843177795</t>
+    <t xml:space="preserve">2.91439867019653</t>
   </si>
   <si>
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
+    <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
     <t xml:space="preserve">2.71697163581848</t>
@@ -53,31 +53,31 @@
     <t xml:space="preserve">2.7451753616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92033624649048</t>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9203360080719</t>
   </si>
   <si>
     <t xml:space="preserve">3.66650152206421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70410680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67590284347534</t>
+    <t xml:space="preserve">3.70410656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67590308189392</t>
   </si>
   <si>
     <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59129095077515</t>
+    <t xml:space="preserve">3.59129118919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.54428482055664</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">3.52548217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.40326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50667953491211</t>
+    <t xml:space="preserve">3.50667977333069</t>
   </si>
   <si>
     <t xml:space="preserve">3.42206835746765</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10242438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24344348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164745330811</t>
+    <t xml:space="preserve">3.10242414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24344372749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22464084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17763471603394</t>
+    <t xml:space="preserve">3.22464108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17763447761536</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">3.45027184486389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608109474182</t>
+    <t xml:space="preserve">3.51608085632324</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8169219493866</t>
+    <t xml:space="preserve">3.92973732948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81692171096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76051425933838</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.71350789070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56308746337891</t>
+    <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
     <t xml:space="preserve">3.65710020065308</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.6853039264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69470548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.73231053352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69470524787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.63849472999573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.61014294624329</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51563692092896</t>
+    <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48728466033936</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">3.76135325431824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585951805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.00706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12992811203003</t>
+    <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.49850273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23565244674683</t>
+    <t xml:space="preserve">5.23565196990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.76488780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697441101074</t>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697393417358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">5.65148019790649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65501546859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69281816482544</t>
+    <t xml:space="preserve">7.88183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65501499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">7.84402799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71171903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831142425537</t>
+    <t xml:space="preserve">7.71171951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831094741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.57941007614136</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">6.97456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99347114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06907558441162</t>
+    <t xml:space="preserve">6.99347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.05017471313477</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.67391681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.392165184021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205257415771</t>
+    <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31655979156494</t>
@@ -374,58 +374,58 @@
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95743560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14644718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91963338851929</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14644813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.01413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86292934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
+    <t xml:space="preserve">7.86292886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">8.60007858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842260360718</t>
+    <t xml:space="preserve">8.07084274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842308044434</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952173233032</t>
+    <t xml:space="preserve">7.74952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.82512617111206</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
+    <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.52270650863647</t>
@@ -443,52 +443,52 @@
     <t xml:space="preserve">7.27698945999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40929889678955</t>
+    <t xml:space="preserve">7.40929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03127384185791</t>
+    <t xml:space="preserve">7.03127336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76665496826172</t>
+    <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
     <t xml:space="preserve">6.65324735641479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
   </si>
   <si>
     <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34314393997192</t>
+    <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24863815307617</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">6.8800630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09742832183838</t>
+    <t xml:space="preserve">7.09742784500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9840202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95566844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68160009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.98401975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9556679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68159961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3319263458252</t>
+    <t xml:space="preserve">6.33192586898804</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">6.35082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11456108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29589080810547</t>
+    <t xml:space="preserve">6.11456155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29589033126831</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">6.73830366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489604949951</t>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">5.97280216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80269002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99170351028442</t>
+    <t xml:space="preserve">5.80269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99170398712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654378890991</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654426574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379787445068</t>
+    <t xml:space="preserve">6.64379692077637</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45478487014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21851873397827</t>
+    <t xml:space="preserve">6.37917900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45478439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027812957764</t>
+    <t xml:space="preserve">6.36027765274048</t>
   </si>
   <si>
     <t xml:space="preserve">6.28467321395874</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
+    <t xml:space="preserve">6.34137678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
   </si>
   <si>
     <t xml:space="preserve">6.26577186584473</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98225259780884</t>
+    <t xml:space="preserve">5.982253074646</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">6.72885274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.275221824646</t>
+    <t xml:space="preserve">6.27522230148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42466497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.547523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71763515472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59477710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67038154602051</t>
+    <t xml:space="preserve">5.77433919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54752349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71763467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59477663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67038202285767</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950620651245</t>
+    <t xml:space="preserve">6.02950572967529</t>
   </si>
   <si>
     <t xml:space="preserve">5.72708511352539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74598693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884498596191</t>
+    <t xml:space="preserve">5.75543737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7459864616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
+    <t xml:space="preserve">5.94444990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.32247591018677</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">6.29412364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18071603775024</t>
+    <t xml:space="preserve">6.18071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675886154175</t>
+    <t xml:space="preserve">6.07675838470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.02005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06730890274048</t>
+    <t xml:space="preserve">6.12401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411588668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.43411540985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
+    <t xml:space="preserve">5.53807306289673</t>
   </si>
   <si>
     <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1978497505188</t>
+    <t xml:space="preserve">5.19785022735596</t>
   </si>
   <si>
     <t xml:space="preserve">5.00883722305298</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.72531795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630542755127</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">4.47960138320923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41817283630371</t>
+    <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">4.63081169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54575634002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57883310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50795364379883</t>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7725715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5457558631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50795316696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773397445679</t>
+    <t xml:space="preserve">4.59773445129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58355808258057</t>
+    <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59300947189331</t>
@@ -875,91 +875,91 @@
     <t xml:space="preserve">4.73476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62608575820923</t>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60718488693237</t>
+    <t xml:space="preserve">4.55520725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.4701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52212905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905229568481</t>
+    <t xml:space="preserve">4.52212953567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.62136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39454555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.3945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597141265869</t>
+    <t xml:space="preserve">4.03542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597093582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036578178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146467208862</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9031126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.92201399803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47487592697144</t>
+    <t xml:space="preserve">4.12520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.44652414321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44179916381836</t>
+    <t xml:space="preserve">4.4417986869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.55993175506592</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
+    <t xml:space="preserve">4.42762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">4.53157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46542596817017</t>
+    <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.51740407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75367021560669</t>
+    <t xml:space="preserve">4.75367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0938925743103</t>
@@ -989,43 +989,43 @@
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9521336555481</t>
+    <t xml:space="preserve">4.92378091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88597917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95213270187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16004705429077</t>
+    <t xml:space="preserve">5.26400470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16004753112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323183059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927560806274</t>
+    <t xml:space="preserve">4.93323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927513122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">4.32839107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43707323074341</t>
+    <t xml:space="preserve">4.43707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24333524703979</t>
+    <t xml:space="preserve">4.21498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24333572387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.01179504394531</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421130180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915571212769</t>
+    <t xml:space="preserve">3.88421154022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915547370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783422470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607459068298</t>
+    <t xml:space="preserve">3.47783398628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">3.3266236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15651226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18486428260803</t>
+    <t xml:space="preserve">3.30772280693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15651249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18486404418945</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">3.14706182479858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794540405273</t>
+    <t xml:space="preserve">3.16596293449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7140998840332</t>
+    <t xml:space="preserve">3.71410012245178</t>
   </si>
   <si>
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476086616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61959338188171</t>
+    <t xml:space="preserve">3.87476062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">3.55343914031982</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.40222883224487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37387681007385</t>
+    <t xml:space="preserve">3.37387704849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.42113018035889</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">3.27937078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26046967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23211741447449</t>
+    <t xml:space="preserve">3.26046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23211765289307</t>
   </si>
   <si>
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035801887512</t>
+    <t xml:space="preserve">3.09035778045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620059967041</t>
+    <t xml:space="preserve">3.01475286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200623512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.10984992980957</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.91847443580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9567494392395</t>
+    <t xml:space="preserve">2.95674967765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92804336547852</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.93761205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59313631057739</t>
+    <t xml:space="preserve">2.7175304889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59313654899597</t>
   </si>
   <si>
     <t xml:space="preserve">2.5070173740387</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.60270524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64098000526428</t>
+    <t xml:space="preserve">2.64098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.62184286117554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744844436646</t>
+    <t xml:space="preserve">2.49744868278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486154556274</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.4400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48787975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47831130027771</t>
+    <t xml:space="preserve">2.48787999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47831106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.41132974624634</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">2.53572392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58356761932373</t>
+    <t xml:space="preserve">2.58356785774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.39219236373901</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.36348605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56442999839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4208984375</t>
+    <t xml:space="preserve">2.56443023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42089867591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.29650473594666</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">1.43531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7989284992218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00944137573242</t>
+    <t xml:space="preserve">1.79892861843109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009441614151</t>
   </si>
   <si>
     <t xml:space="preserve">2.05728554725647</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">1.82285046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62669086456299</t>
+    <t xml:space="preserve">1.6266907453537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58841562271118</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.55970931053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53100299835205</t>
+    <t xml:space="preserve">1.53100311756134</t>
   </si>
   <si>
     <t xml:space="preserve">1.49272787570953</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">1.40660905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48315906524658</t>
+    <t xml:space="preserve">1.48315918445587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6075531244278</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">1.74151599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74630045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7128096818924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68410325050354</t>
+    <t xml:space="preserve">1.74630033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71280956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68410336971283</t>
   </si>
   <si>
     <t xml:space="preserve">1.68888771533966</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">1.64104390144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67931890487671</t>
+    <t xml:space="preserve">1.679319024086</t>
   </si>
   <si>
     <t xml:space="preserve">1.65061271190643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59798431396484</t>
+    <t xml:space="preserve">1.59798443317413</t>
   </si>
   <si>
     <t xml:space="preserve">2.08599185943604</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.85634124279022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073506355286</t>
+    <t xml:space="preserve">1.98073518276215</t>
   </si>
   <si>
     <t xml:space="preserve">1.9041850566864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95202875137329</t>
+    <t xml:space="preserve">1.95202887058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.91375374794006</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.26779818534851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24866056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32521080970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25822925567627</t>
+    <t xml:space="preserve">2.24866080284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32521104812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25822949409485</t>
   </si>
   <si>
     <t xml:space="preserve">2.15297317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19124794006348</t>
+    <t xml:space="preserve">2.19124817848206</t>
   </si>
   <si>
     <t xml:space="preserve">2.17211055755615</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.06685423851013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07642292976379</t>
+    <t xml:space="preserve">2.07642316818237</t>
   </si>
   <si>
     <t xml:space="preserve">2.13383555412292</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.40176105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35391712188721</t>
+    <t xml:space="preserve">2.35391736030579</t>
   </si>
   <si>
     <t xml:space="preserve">2.27736711502075</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.30607342720032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28693580627441</t>
+    <t xml:space="preserve">2.28693604469299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22952318191528</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.23909187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3347795009613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18167924880981</t>
+    <t xml:space="preserve">2.33477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18167948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.20081686973572</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.03814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02857875823975</t>
+    <t xml:space="preserve">2.02857899665833</t>
   </si>
   <si>
     <t xml:space="preserve">2.10512924194336</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">2.14340424537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01901006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04771661758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11469793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09556031227112</t>
+    <t xml:space="preserve">2.01901030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04771685600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1146981716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.93289136886597</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">1.96159768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82763493061066</t>
+    <t xml:space="preserve">1.83720362186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75108480453491</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.67453455924988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64582824707031</t>
+    <t xml:space="preserve">1.6458283662796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65539705753326</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.88504755496979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87069427967072</t>
+    <t xml:space="preserve">1.87069439888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84677231311798</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">1.89461624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86112570762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99030387401581</t>
+    <t xml:space="preserve">1.86112558841705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.94246006011963</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.92332255840302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987256526947</t>
+    <t xml:space="preserve">1.99987268447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.10557866096497</t>
@@ -2091,6 +2091,12 @@
   </si>
   <si>
     <t xml:space="preserve">0.888000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870000004768372</t>
   </si>
 </sst>
 </file>
@@ -36333,7 +36339,7 @@
     </row>
     <row r="1305">
       <c r="A1305" s="1" t="n">
-        <v>46093.5377662037</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B1305" t="n">
         <v>1050</v>
@@ -36354,6 +36360,56 @@
         <v>692</v>
       </c>
       <c r="H1305" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B1306" t="n">
+        <v>12806</v>
+      </c>
+      <c r="C1306" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>0.86599999666214</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>0.888000011444092</v>
+      </c>
+      <c r="F1306"/>
+      <c r="G1306" t="s">
+        <v>693</v>
+      </c>
+      <c r="H1306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46094.6873842593</v>
+      </c>
+      <c r="B1307" t="n">
+        <v>12806</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>0.86599999666214</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>0.888000011444092</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>694</v>
+      </c>
+      <c r="H1307" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="698">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.82085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71697163581848</t>
+    <t xml:space="preserve">2.71697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.74517560005188</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">3.3191237449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">3.92033648490906</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">3.67590284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55368590354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54428458213806</t>
+    <t xml:space="preserve">3.55368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59129095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
     <t xml:space="preserve">3.61009383201599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61949491500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57248830795288</t>
+    <t xml:space="preserve">3.61949515342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57248854637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.52548217773438</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907424926758</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1964373588562</t>
+    <t xml:space="preserve">3.19643712043762</t>
   </si>
   <si>
     <t xml:space="preserve">3.10242414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24344372749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404240608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2246413230896</t>
+    <t xml:space="preserve">3.24344348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27164721488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.17763471603394</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">3.45027208328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81692218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76051425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77931666374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82632374763489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80752062797546</t>
+    <t xml:space="preserve">3.92973756790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8169219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76051449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77931690216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80752086639404</t>
   </si>
   <si>
     <t xml:space="preserve">3.78871846199036</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
+    <t xml:space="preserve">3.65710043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
   </si>
   <si>
     <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68530440330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73231029510498</t>
+    <t xml:space="preserve">3.68530416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73231053352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470548629761</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014294624329</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
+    <t xml:space="preserve">3.76135301589966</t>
   </si>
   <si>
     <t xml:space="preserve">3.78025460243225</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">3.80860662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85585975646973</t>
+    <t xml:space="preserve">3.85585951805115</t>
   </si>
   <si>
     <t xml:space="preserve">4.04487276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23565196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76488780975342</t>
+    <t xml:space="preserve">4.4985032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23565244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76488828659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.48136949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46246767044067</t>
+    <t xml:space="preserve">5.46246814727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.51917171478271</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65501499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.65501546859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59831142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.97456979751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67391681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80622529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.392165184021</t>
+    <t xml:space="preserve">7.67391633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">8.12754726409912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03304004669189</t>
+    <t xml:space="preserve">8.03304100036621</t>
   </si>
   <si>
     <t xml:space="preserve">7.95743608474731</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523782730103</t>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.90073204040527</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">7.42820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60007858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07084274291992</t>
+    <t xml:space="preserve">8.60007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
     <t xml:space="preserve">7.93853425979614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76842308044434</t>
+    <t xml:space="preserve">7.76842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.74952173233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">7.61721324920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40929937362671</t>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">7.33369398117065</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
+    <t xml:space="preserve">6.65324783325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.18248319625854</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68159961700439</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
     <t xml:space="preserve">6.61544561386108</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">6.44533395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29589033126831</t>
+    <t xml:space="preserve">7.29589080810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.12577962875366</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">5.78378915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170398712158</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">6.52093887329102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64379692077637</t>
+    <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37917900085449</t>
+    <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.45478439331055</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">6.23741960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36027765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28467321395874</t>
+    <t xml:space="preserve">6.36027812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">6.2279691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34137678146362</t>
+    <t xml:space="preserve">6.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.31302499771118</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">6.00115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.982253074646</t>
+    <t xml:space="preserve">5.98225259780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.96335124969482</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42466449737549</t>
+    <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
     <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71763467788696</t>
+    <t xml:space="preserve">5.71763515472412</t>
   </si>
   <si>
     <t xml:space="preserve">5.59477663040161</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67038202285767</t>
+    <t xml:space="preserve">5.67038154602051</t>
   </si>
   <si>
     <t xml:space="preserve">5.62312841415405</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">5.70818424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
   </si>
   <si>
     <t xml:space="preserve">5.84994411468506</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">5.9539008140564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75543737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7459864616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86884450912476</t>
+    <t xml:space="preserve">5.75543785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.90664768218994</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">6.32247591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.5758752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43411540985107</t>
+    <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
     <t xml:space="preserve">5.47191858291626</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -824,40 +824,40 @@
     <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53630542755127</t>
+    <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.45124959945679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
+    <t xml:space="preserve">4.63081216812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.67333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7725715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5457558631897</t>
+    <t xml:space="preserve">4.77257204055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50795316696167</t>
+    <t xml:space="preserve">4.50795364379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59773445129395</t>
+    <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.60245990753174</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">4.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52212953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51267910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.60718488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47015142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52212905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51267862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">4.25751161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02597093582153</t>
+    <t xml:space="preserve">4.03542184829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02597141265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.092125415802</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">3.95036602020264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9031126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92201399803162</t>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
   </si>
   <si>
     <t xml:space="preserve">3.95509099960327</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">4.46542549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75367069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92378091812134</t>
+    <t xml:space="preserve">4.9237813949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.88597917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213270187378</t>
+    <t xml:space="preserve">4.95213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">5.03718900680542</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82927513122559</t>
+    <t xml:space="preserve">4.93323183059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82927560806274</t>
   </si>
   <si>
     <t xml:space="preserve">4.85762691497803</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.34729242324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21498346328735</t>
+    <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
     <t xml:space="preserve">4.27168798446655</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">3.84168362617493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79915547370911</t>
+    <t xml:space="preserve">3.88421177864075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79915571212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.77080392837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47783398628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360743522644</t>
+    <t xml:space="preserve">3.47783422470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21321630477905</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">3.24156832695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3266236782074</t>
+    <t xml:space="preserve">3.32662391662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.30772280693054</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">3.15651249885559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18486404418945</t>
+    <t xml:space="preserve">3.18486428260803</t>
   </si>
   <si>
     <t xml:space="preserve">3.11870980262756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14706182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16596293449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64794516563416</t>
+    <t xml:space="preserve">3.14706158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1659631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.66684699058533</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.05432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476062774658</t>
+    <t xml:space="preserve">3.87476086616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.61959362030029</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.20376586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09035778045654</t>
+    <t xml:space="preserve">3.09035801887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.04310488700867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02420353889465</t>
+    <t xml:space="preserve">3.02420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">2.92969703674316</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">2.9769504070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01475286483765</t>
+    <t xml:space="preserve">3.01475310325623</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200623512268</t>
@@ -2099,10 +2099,13 @@
     <t xml:space="preserve">0.870000004768372</t>
   </si>
   <si>
+    <t xml:space="preserve">0.878000020980835</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">0.878000020980835</t>
+    <t xml:space="preserve">0.867999970912933</t>
   </si>
 </sst>
 </file>
@@ -36411,7 +36414,9 @@
       <c r="E1307" t="n">
         <v>0.878000020980835</v>
       </c>
-      <c r="F1307"/>
+      <c r="F1307" t="n">
+        <v>0.878000020980835</v>
+      </c>
       <c r="G1307" t="s">
         <v>695</v>
       </c>
@@ -36421,27 +36426,51 @@
     </row>
     <row r="1308">
       <c r="A1308" s="1" t="n">
-        <v>46097.6253125</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B1308" t="n">
-        <v>100</v>
+        <v>12604</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.878000020980835</v>
+        <v>0.870000004768372</v>
       </c>
       <c r="D1308" t="n">
-        <v>0.878000020980835</v>
+        <v>0.833999991416931</v>
       </c>
       <c r="E1308" t="n">
-        <v>0.878000020980835</v>
-      </c>
-      <c r="F1308" t="n">
-        <v>0.878000020980835</v>
-      </c>
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1308"/>
       <c r="G1308" t="s">
         <v>696</v>
       </c>
       <c r="H1308" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46098.5226851852</v>
+      </c>
+      <c r="B1309" t="n">
+        <v>12604</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="G1309" t="s">
+        <v>697</v>
+      </c>
+      <c r="H1309" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="698">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">VNT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82085561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74517560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31912398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90153360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9203360080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66650176048279</t>
+    <t xml:space="preserve">2.82085585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71697163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7451753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90153384208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92033648490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66650128364563</t>
   </si>
   <si>
     <t xml:space="preserve">3.70410656929016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67590260505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55368614196777</t>
+    <t xml:space="preserve">3.67590284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55368590354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.59129118919373</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">3.54428482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61009335517883</t>
+    <t xml:space="preserve">3.61009359359741</t>
   </si>
   <si>
     <t xml:space="preserve">3.61949491500854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57248878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254819393158</t>
+    <t xml:space="preserve">3.57248830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52548241615295</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.42206811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46907448768616</t>
+    <t xml:space="preserve">3.46907472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.41266679763794</t>
@@ -116,52 +116,52 @@
     <t xml:space="preserve">3.25284481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19643759727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10242414474487</t>
+    <t xml:space="preserve">3.19643712043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10242438316345</t>
   </si>
   <si>
     <t xml:space="preserve">3.24344372749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27164769172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23404216766357</t>
+    <t xml:space="preserve">3.27164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23404240608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.22464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17763495445251</t>
+    <t xml:space="preserve">3.17763471603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.29985117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45027184486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51608085632324</t>
+    <t xml:space="preserve">3.45027208328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51608109474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60069227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92973732948303</t>
+    <t xml:space="preserve">3.92973685264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.8169219493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76051425933838</t>
+    <t xml:space="preserve">3.7605140209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.77931690216064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82632374763489</t>
+    <t xml:space="preserve">3.82632350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.80752086639404</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.78871822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76991558074951</t>
+    <t xml:space="preserve">3.76991581916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.71350789070129</t>
@@ -179,34 +179,34 @@
     <t xml:space="preserve">3.56308722496033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65710043907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6288959980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72290897369385</t>
+    <t xml:space="preserve">3.65710020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62889623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72290921211243</t>
   </si>
   <si>
     <t xml:space="preserve">3.68530416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73231077194214</t>
+    <t xml:space="preserve">3.73231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69470524787903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72355079650879</t>
+    <t xml:space="preserve">3.72355055809021</t>
   </si>
   <si>
     <t xml:space="preserve">3.65739607810974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61014318466187</t>
+    <t xml:space="preserve">3.63849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61014270782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54398846626282</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.51563668251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48728466033936</t>
+    <t xml:space="preserve">3.48728489875793</t>
   </si>
   <si>
     <t xml:space="preserve">3.67629766464233</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">3.57234048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59124183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62904405593872</t>
+    <t xml:space="preserve">3.59124159812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6290442943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.73300123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76135325431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78025436401367</t>
+    <t xml:space="preserve">3.76135301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78025460243225</t>
   </si>
   <si>
     <t xml:space="preserve">3.74245190620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80860638618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85585927963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00706911087036</t>
+    <t xml:space="preserve">3.80860662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85585951805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04487276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.12992763519287</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">5.23565244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76488780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48136901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55697393417358</t>
+    <t xml:space="preserve">5.76488828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48136949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50027084350586</t>
+    <t xml:space="preserve">5.5002703666687</t>
   </si>
   <si>
     <t xml:space="preserve">5.46246814727783</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">5.51917171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68928289413452</t>
+    <t xml:space="preserve">5.65148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68928337097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.16358184814453</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">7.14468097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8818302154541</t>
+    <t xml:space="preserve">7.88183116912842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65501546859741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71171855926514</t>
+    <t xml:space="preserve">7.69281816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84402894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71171903610229</t>
   </si>
   <si>
     <t xml:space="preserve">7.59831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57941007614136</t>
+    <t xml:space="preserve">7.57941055297852</t>
   </si>
   <si>
     <t xml:space="preserve">7.54160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99347066879272</t>
+    <t xml:space="preserve">6.97456979751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99347114562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.06907606124878</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.48490381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78732395172119</t>
+    <t xml:space="preserve">7.78732442855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.46600246429443</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">7.67391633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80622625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39216423034668</t>
+    <t xml:space="preserve">7.80622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39216613769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.29765796661377</t>
@@ -365,82 +365,82 @@
     <t xml:space="preserve">8.22205352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37326335906982</t>
+    <t xml:space="preserve">8.31656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37326431274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.957435131073</t>
+    <t xml:space="preserve">8.12754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03304100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">8.14644813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99523830413818</t>
+    <t xml:space="preserve">7.99523878097534</t>
   </si>
   <si>
     <t xml:space="preserve">7.91963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86292886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90073108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44710159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42819976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60007858276367</t>
+    <t xml:space="preserve">8.01413917541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86292934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5605092048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44710111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60007953643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.07084369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93853378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73062086105347</t>
+    <t xml:space="preserve">7.93853425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76842355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73062038421631</t>
   </si>
   <si>
     <t xml:space="preserve">7.74952173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82512617111206</t>
+    <t xml:space="preserve">7.82512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.6361141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52270650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27698945999146</t>
+    <t xml:space="preserve">7.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40929889678955</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.33369398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25808811187744</t>
+    <t xml:space="preserve">7.2580885887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08797693252563</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.01237201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46423482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63434648513794</t>
+    <t xml:space="preserve">6.46423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6343469619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.70995187759399</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">6.76665544509888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65324735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37149667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43765068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39039707183838</t>
+    <t xml:space="preserve">6.65324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18248319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37149620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43765020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39039754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.34314441680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24863767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88951396942139</t>
+    <t xml:space="preserve">7.24863815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88951349258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.8800630569458</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.11632919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9556679725647</t>
+    <t xml:space="preserve">6.9840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95566844940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68160009384155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61544513702393</t>
+    <t xml:space="preserve">6.61544561386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.56819200515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70050096511841</t>
+    <t xml:space="preserve">6.70050144195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.53984022140503</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">6.51148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33192586898804</t>
+    <t xml:space="preserve">6.3319263458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.41698217391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44533443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35082721710205</t>
+    <t xml:space="preserve">6.44533395767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35082769393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.11456155776978</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">6.6059947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58709335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62489557266235</t>
+    <t xml:space="preserve">6.73830366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58709287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62489652633667</t>
   </si>
   <si>
     <t xml:space="preserve">6.38863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78378963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03895616531372</t>
+    <t xml:space="preserve">5.78378915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03895664215088</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939407348633</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">5.89719676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97280263900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88774585723877</t>
+    <t xml:space="preserve">5.97280216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88774633407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.52862215042114</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">5.80269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99170303344727</t>
+    <t xml:space="preserve">5.99170351028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.25632095336914</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.13346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52093935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59654426574707</t>
+    <t xml:space="preserve">6.52093887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">6.75720500946045</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">6.64379739761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4736852645874</t>
+    <t xml:space="preserve">6.47368574142456</t>
   </si>
   <si>
     <t xml:space="preserve">6.37917947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45478487014771</t>
+    <t xml:space="preserve">6.45478439331055</t>
   </si>
   <si>
     <t xml:space="preserve">6.21851825714111</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">6.36027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28467321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22796964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34137678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26577234268188</t>
+    <t xml:space="preserve">6.28467273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34137725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31302499771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00115346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04840707778931</t>
+    <t xml:space="preserve">6.00115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04840755462646</t>
   </si>
   <si>
     <t xml:space="preserve">6.08620977401733</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">6.24687051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.774338722229</t>
+    <t xml:space="preserve">5.77433919906616</t>
   </si>
   <si>
     <t xml:space="preserve">5.42466497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.547523021698</t>
+    <t xml:space="preserve">5.54752349853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.71763515472412</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">5.59477663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64202976226807</t>
+    <t xml:space="preserve">5.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.67038154602051</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">5.62312841415405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70818376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73653602600098</t>
+    <t xml:space="preserve">5.70818424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73653650283813</t>
   </si>
   <si>
     <t xml:space="preserve">5.81214141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8499436378479</t>
+    <t xml:space="preserve">6.02950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84994411468506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9539008140564</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.75543785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7459864616394</t>
+    <t xml:space="preserve">5.74598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86884498596191</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">5.90664768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32247543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29412364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18071556091309</t>
+    <t xml:space="preserve">5.94444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32247591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29412317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18071603775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.16181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07675933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02005481719971</t>
+    <t xml:space="preserve">6.07675886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02005529403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.12401247024536</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">5.79324007034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56642484664917</t>
+    <t xml:space="preserve">5.56642436981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.5758752822876</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">5.43411588668823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4719181060791</t>
+    <t xml:space="preserve">5.47191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.50972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53807258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31125783920288</t>
+    <t xml:space="preserve">5.53807306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">5.19785022735596</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.86707782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81037378311157</t>
+    <t xml:space="preserve">4.81037425994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.7158670425415</t>
@@ -812,40 +812,40 @@
     <t xml:space="preserve">4.70641660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70169115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72531843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72059297561646</t>
+    <t xml:space="preserve">4.70169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72531795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7205924987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.53630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45124912261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47960138320923</t>
+    <t xml:space="preserve">4.45124959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">4.41817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63081169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67333936691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77257108688354</t>
+    <t xml:space="preserve">4.63081216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.54575634002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57883310317993</t>
+    <t xml:space="preserve">4.57883262634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.50795364379883</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">4.59773397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60245943069458</t>
+    <t xml:space="preserve">4.60245990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.58355855941772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61191034317017</t>
+    <t xml:space="preserve">4.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.65916347503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73476934432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62608623504639</t>
+    <t xml:space="preserve">4.73476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62608671188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.56465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55520677566528</t>
+    <t xml:space="preserve">4.55520725250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.60718488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4701509475708</t>
+    <t xml:space="preserve">4.47015142440796</t>
   </si>
   <si>
     <t xml:space="preserve">4.52212905883789</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">4.51267862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48905181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62136077880859</t>
+    <t xml:space="preserve">4.48905229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62136125564575</t>
   </si>
   <si>
     <t xml:space="preserve">4.3945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3425669670105</t>
+    <t xml:space="preserve">4.34256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">4.25751161575317</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">4.092125415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95036554336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90311312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9220142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95509123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94091510772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96926689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06377410888672</t>
+    <t xml:space="preserve">4.08739995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95036602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92201447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95509099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94091558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96926712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06377363204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.10157632827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12520217895508</t>
+    <t xml:space="preserve">4.12520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.47487640380859</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42762327194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53157949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46542596817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51740407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75366973876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0938925743103</t>
+    <t xml:space="preserve">4.42762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46542549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51740455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75367021560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09389305114746</t>
   </si>
   <si>
     <t xml:space="preserve">4.98048543930054</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.03718900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98993635177612</t>
+    <t xml:space="preserve">4.98993587493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.04663991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26400423049927</t>
+    <t xml:space="preserve">5.26400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.16004753112793</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.17894887924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01828813552856</t>
+    <t xml:space="preserve">5.01828765869141</t>
   </si>
   <si>
     <t xml:space="preserve">5.02773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93323135375977</t>
+    <t xml:space="preserve">4.93323183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.82927560806274</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.38509511947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32839107513428</t>
+    <t xml:space="preserve">4.32839155197144</t>
   </si>
   <si>
     <t xml:space="preserve">4.43707370758057</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preser